--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_npcShop.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_npcShop.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_npcShop" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_npcShop!$A$1:$S$4</definedName>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="118">
   <si>
     <t>序号</t>
   </si>
@@ -537,6 +538,9 @@
     <t>10010002#2#0#100</t>
   </si>
   <si>
+    <t>大量苹果</t>
+  </si>
+  <si>
     <t>小瓶治疗药水</t>
   </si>
   <si>
@@ -546,7 +550,37 @@
     <t>10010002#50#0#100</t>
   </si>
   <si>
-    <t>小型精华治疗药水</t>
+    <t>中瓶治疗药水</t>
+  </si>
+  <si>
+    <t>10010002#80#0#100</t>
+  </si>
+  <si>
+    <t>大瓶治疗药水</t>
+  </si>
+  <si>
+    <t>10010002#100#0#100</t>
+  </si>
+  <si>
+    <t>超大治疗药水</t>
+  </si>
+  <si>
+    <t>10010002#150#0#100</t>
+  </si>
+  <si>
+    <t>小瓶魔力药水</t>
+  </si>
+  <si>
+    <t>中瓶魔力药水</t>
+  </si>
+  <si>
+    <t>大瓶魔力药水</t>
+  </si>
+  <si>
+    <t>10010002#200#0#100</t>
+  </si>
+  <si>
+    <t>精华魔力药水</t>
   </si>
   <si>
     <r>
@@ -575,37 +609,13 @@
     </r>
   </si>
   <si>
-    <t>小瓶魔力药水</t>
-  </si>
-  <si>
-    <t>精华魔力药水</t>
-  </si>
-  <si>
-    <t>中瓶治疗药水</t>
-  </si>
-  <si>
-    <t>101#50</t>
-  </si>
-  <si>
-    <t>10010002#80#0#100</t>
+    <t>小型精华治疗药水</t>
   </si>
   <si>
     <t>中型精华治疗药水</t>
   </si>
   <si>
     <t>10010002#1000#0#100</t>
-  </si>
-  <si>
-    <t>中瓶魔力药水</t>
-  </si>
-  <si>
-    <t>10010002#100#0#100</t>
-  </si>
-  <si>
-    <t>大瓶治疗药水</t>
-  </si>
-  <si>
-    <t>101#100</t>
   </si>
   <si>
     <t>大型精华治疗药水</t>
@@ -637,21 +647,6 @@
     </r>
   </si>
   <si>
-    <t>大瓶魔力药水</t>
-  </si>
-  <si>
-    <t>10010002#200#0#100</t>
-  </si>
-  <si>
-    <t>超大治疗药水</t>
-  </si>
-  <si>
-    <t>101#200</t>
-  </si>
-  <si>
-    <t>10010002#150#0#100</t>
-  </si>
-  <si>
     <t>超大精华治疗药水</t>
   </si>
   <si>
@@ -681,78 +676,99 @@
     </r>
   </si>
   <si>
-    <t>大量苹果</t>
-  </si>
-  <si>
     <t>大量小瓶治疗药水</t>
   </si>
   <si>
     <t>大量中瓶治疗药水</t>
   </si>
   <si>
+    <t>大量大瓶治疗药水</t>
+  </si>
+  <si>
+    <t>大量超大治疗药水</t>
+  </si>
+  <si>
+    <t>10010002#400#0#100</t>
+  </si>
+  <si>
+    <t>大量小型精华治疗药水</t>
+  </si>
+  <si>
+    <t>10010002#10#0#100</t>
+  </si>
+  <si>
+    <t>大量中型精华治疗药水</t>
+  </si>
+  <si>
+    <t>10010002#10.8#0#100</t>
+  </si>
+  <si>
+    <t>大量大型精华治疗药水</t>
+  </si>
+  <si>
+    <t>10010002#11.5#0#100</t>
+  </si>
+  <si>
+    <t>大量超大精华治疗药水</t>
+  </si>
+  <si>
+    <t>10010002#12#0#100</t>
+  </si>
+  <si>
+    <t>大量小瓶魔力药水</t>
+  </si>
+  <si>
+    <t>大量中瓶魔力药水</t>
+  </si>
+  <si>
+    <t>10010002#5#0#100</t>
+  </si>
+  <si>
+    <t>大量大瓶魔力药水</t>
+  </si>
+  <si>
+    <t>10010002#7.7#0#100</t>
+  </si>
+  <si>
+    <t>大量精华魔力药水</t>
+  </si>
+  <si>
+    <t>10010002#8.5#0#100</t>
+  </si>
+  <si>
+    <t>战斗箭筒</t>
+  </si>
+  <si>
+    <t>10010002#2000#0#100</t>
+  </si>
+  <si>
+    <t>多重箭之石</t>
+  </si>
+  <si>
+    <t>冲击技能书</t>
+  </si>
+  <si>
+    <t>冲击波卷轴</t>
+  </si>
+  <si>
+    <t>101#50</t>
+  </si>
+  <si>
+    <t>101#100</t>
+  </si>
+  <si>
+    <t>101#200</t>
+  </si>
+  <si>
     <t>101#70</t>
   </si>
   <si>
-    <t>大量大瓶治疗药水</t>
-  </si>
-  <si>
     <t>101#150</t>
   </si>
   <si>
-    <t>大量超大治疗药水</t>
-  </si>
-  <si>
     <t>101#250</t>
   </si>
   <si>
-    <t>10010002#400#0#100</t>
-  </si>
-  <si>
-    <t>大量小型精华治疗药水</t>
-  </si>
-  <si>
-    <t>10010002#10#0#100</t>
-  </si>
-  <si>
-    <t>大量中型精华治疗药水</t>
-  </si>
-  <si>
-    <t>10010002#10.8#0#100</t>
-  </si>
-  <si>
-    <t>大量大型精华治疗药水</t>
-  </si>
-  <si>
-    <t>10010002#11.5#0#100</t>
-  </si>
-  <si>
-    <t>大量超大精华治疗药水</t>
-  </si>
-  <si>
-    <t>10010002#12#0#100</t>
-  </si>
-  <si>
-    <t>大量小瓶魔力药水</t>
-  </si>
-  <si>
-    <t>大量中瓶魔力药水</t>
-  </si>
-  <si>
-    <t>10010002#5#0#100</t>
-  </si>
-  <si>
-    <t>大量大瓶魔力药水</t>
-  </si>
-  <si>
-    <t>10010002#7.7#0#100</t>
-  </si>
-  <si>
-    <t>大量精华魔力药水</t>
-  </si>
-  <si>
-    <t>10010002#8.5#0#100</t>
-  </si>
-  <si>
     <t>皮盔</t>
   </si>
   <si>
@@ -801,9 +817,6 @@
     <t>瞬间移动术</t>
   </si>
   <si>
-    <t>10010002#2000#0#100</t>
-  </si>
-  <si>
     <t>陨石术</t>
   </si>
   <si>
@@ -841,9 +854,6 @@
   </si>
   <si>
     <t>暗黑骑士召唤之石</t>
-  </si>
-  <si>
-    <t>战斗箭筒</t>
   </si>
 </sst>
 </file>
@@ -864,15 +874,15 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1043,12 +1053,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1346,19 +1362,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1367,7 +1383,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1391,16 +1407,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1409,106 +1425,103 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1528,6 +1541,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2089,2388 +2114,2132 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="31.2857142857143" style="2" customWidth="1"/>
-    <col min="3" max="3" width="21.1428571428571" style="2" customWidth="1"/>
-    <col min="4" max="4" width="65.1428571428571" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24" style="2" customWidth="1"/>
-    <col min="6" max="6" width="45.7142857142857" style="2" customWidth="1"/>
-    <col min="7" max="7" width="54.4285714285714" style="2" customWidth="1"/>
-    <col min="8" max="8" width="41" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.8571428571429" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9" style="2"/>
-    <col min="11" max="12" width="10.5714285714286" style="2"/>
-    <col min="13" max="13" width="9.57142857142857" style="2"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="31.2857142857143" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.1428571428571" style="1" customWidth="1"/>
+    <col min="4" max="4" width="65.1428571428571" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24" style="1" customWidth="1"/>
+    <col min="6" max="6" width="45.7142857142857" style="1" customWidth="1"/>
+    <col min="7" max="7" width="54.4285714285714" style="1" customWidth="1"/>
+    <col min="8" max="8" width="41" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.8571428571429" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1"/>
+    <col min="11" max="12" width="10.5714285714286" style="1"/>
+    <col min="13" max="13" width="9.57142857142857" style="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="20.1" customHeight="1" spans="1:19">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:19">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>100</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>30010001</v>
       </c>
-      <c r="C5" s="2">
-        <v>20</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="C5" s="1">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="G5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:19">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>101</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
+        <v>30010001</v>
+      </c>
+      <c r="C6" s="1">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="N6" s="6"/>
+      <c r="S6" s="6"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:19">
+      <c r="A7" s="1">
+        <v>102</v>
+      </c>
+      <c r="B7" s="5">
         <v>30010002</v>
       </c>
-      <c r="C6" s="2">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="C7" s="1">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:19">
+      <c r="A8" s="1">
+        <v>103</v>
+      </c>
+      <c r="B8" s="5">
+        <v>30010003</v>
+      </c>
+      <c r="C8" s="1">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:19">
+      <c r="A9" s="1">
+        <v>104</v>
+      </c>
+      <c r="B9" s="5">
+        <v>30010004</v>
+      </c>
+      <c r="C9" s="1">
+        <v>20</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:19">
+      <c r="A10" s="1">
+        <v>105</v>
+      </c>
+      <c r="B10" s="5">
+        <v>30010005</v>
+      </c>
+      <c r="C10" s="1">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="8"/>
+      <c r="N10" s="6"/>
+      <c r="S10" s="6"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:19">
+      <c r="A11" s="1">
+        <v>106</v>
+      </c>
+      <c r="B11" s="5">
+        <v>30010012</v>
+      </c>
+      <c r="C11" s="1">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="6"/>
+      <c r="S11" s="6"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:19">
+      <c r="A12" s="1">
+        <v>107</v>
+      </c>
+      <c r="B12" s="5">
+        <v>30010013</v>
+      </c>
+      <c r="C12" s="1">
+        <v>20</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="6"/>
+      <c r="S12" s="6"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:19">
+      <c r="A13" s="1">
+        <v>108</v>
+      </c>
+      <c r="B13" s="5">
+        <v>30010014</v>
+      </c>
+      <c r="C13" s="1">
+        <v>20</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="6"/>
+      <c r="S13" s="6"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:19">
+      <c r="A14" s="1">
+        <v>109</v>
+      </c>
+      <c r="B14" s="5">
+        <v>30010015</v>
+      </c>
+      <c r="C14" s="1">
+        <v>20</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="6"/>
+      <c r="S14" s="6"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:19">
+      <c r="A15" s="1">
+        <v>110</v>
+      </c>
+      <c r="B15" s="5">
+        <v>30010006</v>
+      </c>
+      <c r="C15" s="1">
+        <v>20</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="S15" s="6"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:19">
+      <c r="A16" s="1">
+        <v>111</v>
+      </c>
+      <c r="B16" s="5">
+        <v>30010007</v>
+      </c>
+      <c r="C16" s="1">
+        <v>20</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="6"/>
+      <c r="S16" s="6"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:19">
+      <c r="A17" s="1">
+        <v>112</v>
+      </c>
+      <c r="B17" s="5">
+        <v>30010008</v>
+      </c>
+      <c r="C17" s="1">
+        <v>20</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="8"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="6"/>
+      <c r="S17" s="6"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:19">
+      <c r="A18" s="1">
+        <v>113</v>
+      </c>
+      <c r="B18" s="5">
+        <v>30010009</v>
+      </c>
+      <c r="C18" s="1">
+        <v>20</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="6"/>
+      <c r="S18" s="6"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:19">
+      <c r="A19" s="1">
+        <v>114</v>
+      </c>
+      <c r="B19" s="5">
+        <v>30010002</v>
+      </c>
+      <c r="C19" s="1">
+        <v>20</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="N19" s="6"/>
+      <c r="S19" s="6"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:19">
+      <c r="A20" s="1">
+        <v>115</v>
+      </c>
+      <c r="B20" s="5">
+        <v>30010003</v>
+      </c>
+      <c r="C20" s="1">
+        <v>20</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="N20" s="6"/>
+      <c r="S20" s="6"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:19">
+      <c r="A21" s="1">
+        <v>116</v>
+      </c>
+      <c r="B21" s="5">
+        <v>30010004</v>
+      </c>
+      <c r="C21" s="1">
+        <v>20</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="N21" s="6"/>
+      <c r="S21" s="6"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:19">
+      <c r="A22" s="1">
+        <v>117</v>
+      </c>
+      <c r="B22" s="5">
+        <v>30010005</v>
+      </c>
+      <c r="C22" s="1">
+        <v>20</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="N22" s="6"/>
+      <c r="S22" s="6"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:19">
+      <c r="A23" s="1">
+        <v>118</v>
+      </c>
+      <c r="B23" s="5">
+        <v>30010006</v>
+      </c>
+      <c r="C23" s="1">
+        <v>20</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="N23" s="6"/>
+      <c r="S23" s="6"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:19">
+      <c r="A24" s="1">
+        <v>119</v>
+      </c>
+      <c r="B24" s="5">
+        <v>30010007</v>
+      </c>
+      <c r="C24" s="1">
+        <v>20</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="N24" s="6"/>
+      <c r="S24" s="6"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:19">
+      <c r="A25" s="1">
+        <v>120</v>
+      </c>
+      <c r="B25" s="5">
+        <v>30010008</v>
+      </c>
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="N25" s="6"/>
+      <c r="S25" s="6"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:19">
+      <c r="A26" s="1">
+        <v>121</v>
+      </c>
+      <c r="B26" s="5">
+        <v>30010009</v>
+      </c>
+      <c r="C26" s="1">
+        <v>20</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="N26" s="6"/>
+      <c r="S26" s="6"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:19">
+      <c r="A27" s="1">
+        <v>122</v>
+      </c>
+      <c r="B27" s="5">
+        <v>30010012</v>
+      </c>
+      <c r="C27" s="1">
+        <v>20</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2</v>
+      </c>
+      <c r="N27" s="6"/>
+      <c r="S27" s="6"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:19">
+      <c r="A28" s="1">
+        <v>123</v>
+      </c>
+      <c r="B28" s="5">
+        <v>30010013</v>
+      </c>
+      <c r="C28" s="1">
+        <v>20</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28" s="1">
+        <v>2</v>
+      </c>
+      <c r="N28" s="6"/>
+      <c r="S28" s="6"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:19">
+      <c r="A29" s="1">
+        <v>124</v>
+      </c>
+      <c r="B29" s="5">
+        <v>30010014</v>
+      </c>
+      <c r="C29" s="1">
+        <v>20</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" s="1">
+        <v>2</v>
+      </c>
+      <c r="N29" s="6"/>
+      <c r="S29" s="6"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:19">
+      <c r="A30" s="1">
+        <v>125</v>
+      </c>
+      <c r="B30" s="5">
+        <v>30010015</v>
+      </c>
+      <c r="C30" s="1">
+        <v>20</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2</v>
+      </c>
+      <c r="N30" s="6"/>
+      <c r="S30" s="6"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:19">
+      <c r="A31" s="1">
+        <v>126</v>
+      </c>
+      <c r="B31" s="5">
+        <v>30010015</v>
+      </c>
+      <c r="C31" s="1">
+        <v>20</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I31" s="1">
+        <v>2</v>
+      </c>
+      <c r="J31" s="7"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="6"/>
+      <c r="S31" s="6"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:19">
+      <c r="A32" s="1">
+        <v>127</v>
+      </c>
+      <c r="B32" s="1">
+        <v>3000104</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:19">
+      <c r="A33" s="1">
+        <v>128</v>
+      </c>
+      <c r="B33" s="14">
+        <v>60030067</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:19">
+      <c r="A34" s="1">
+        <v>129</v>
+      </c>
+      <c r="B34" s="14">
+        <v>60030072</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:19">
+      <c r="A35" s="1">
+        <v>130</v>
+      </c>
+      <c r="B35" s="5">
+        <v>30010001</v>
+      </c>
+      <c r="C35" s="1">
+        <v>20</v>
+      </c>
+      <c r="D35" s="1">
+        <v>5</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="1:19">
+      <c r="A36" s="1">
+        <v>131</v>
+      </c>
+      <c r="B36" s="5">
+        <v>30010001</v>
+      </c>
+      <c r="C36" s="1">
+        <v>20</v>
+      </c>
+      <c r="D36" s="1">
+        <v>5</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F36" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="N36" s="6"/>
+      <c r="S36" s="6"/>
+    </row>
+    <row r="37" ht="16.5" spans="1:19">
+      <c r="A37" s="1">
+        <v>132</v>
+      </c>
+      <c r="B37" s="5">
+        <v>30010002</v>
+      </c>
+      <c r="C37" s="1">
+        <v>20</v>
+      </c>
+      <c r="D37" s="1">
+        <v>5</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="F37" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:19">
-      <c r="A7" s="2">
-        <v>102</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="G37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:19">
+      <c r="A38" s="1">
+        <v>133</v>
+      </c>
+      <c r="B38" s="5">
+        <v>30010003</v>
+      </c>
+      <c r="C38" s="1">
+        <v>20</v>
+      </c>
+      <c r="D38" s="1">
+        <v>5</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:19">
+      <c r="A39" s="1">
+        <v>134</v>
+      </c>
+      <c r="B39" s="5">
+        <v>30010004</v>
+      </c>
+      <c r="C39" s="1">
+        <v>20</v>
+      </c>
+      <c r="D39" s="1">
+        <v>5</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="1:19">
+      <c r="A40" s="1">
+        <v>135</v>
+      </c>
+      <c r="B40" s="5">
+        <v>30010005</v>
+      </c>
+      <c r="C40" s="1">
+        <v>20</v>
+      </c>
+      <c r="D40" s="1">
+        <v>5</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="M40" s="8"/>
+      <c r="N40" s="6"/>
+      <c r="S40" s="6"/>
+    </row>
+    <row r="41" ht="16.5" spans="1:19">
+      <c r="A41" s="1">
+        <v>136</v>
+      </c>
+      <c r="B41" s="5">
+        <v>30010012</v>
+      </c>
+      <c r="C41" s="1">
+        <v>20</v>
+      </c>
+      <c r="D41" s="1">
+        <v>5</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I41" s="1">
+        <v>2</v>
+      </c>
+      <c r="J41" s="7"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="6"/>
+      <c r="S41" s="6"/>
+    </row>
+    <row r="42" ht="16.5" spans="1:19">
+      <c r="A42" s="1">
+        <v>137</v>
+      </c>
+      <c r="B42" s="5">
+        <v>30010013</v>
+      </c>
+      <c r="C42" s="1">
+        <v>20</v>
+      </c>
+      <c r="D42" s="1">
+        <v>5</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I42" s="1">
+        <v>2</v>
+      </c>
+      <c r="J42" s="7"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="6"/>
+      <c r="S42" s="6"/>
+    </row>
+    <row r="43" ht="16.5" spans="1:19">
+      <c r="A43" s="1">
+        <v>138</v>
+      </c>
+      <c r="B43" s="5">
+        <v>30010014</v>
+      </c>
+      <c r="C43" s="1">
+        <v>20</v>
+      </c>
+      <c r="D43" s="1">
+        <v>5</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I43" s="1">
+        <v>2</v>
+      </c>
+      <c r="J43" s="7"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7"/>
+      <c r="N43" s="6"/>
+      <c r="S43" s="6"/>
+    </row>
+    <row r="44" ht="16.5" spans="1:19">
+      <c r="A44" s="1">
+        <v>139</v>
+      </c>
+      <c r="B44" s="5">
+        <v>30010015</v>
+      </c>
+      <c r="C44" s="1">
+        <v>20</v>
+      </c>
+      <c r="D44" s="1">
+        <v>5</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I44" s="1">
+        <v>2</v>
+      </c>
+      <c r="J44" s="7"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7"/>
+      <c r="N44" s="6"/>
+      <c r="S44" s="6"/>
+    </row>
+    <row r="45" ht="16.5" spans="1:19">
+      <c r="A45" s="1">
+        <v>140</v>
+      </c>
+      <c r="B45" s="5">
         <v>30010006</v>
       </c>
-      <c r="C7" s="2">
-        <v>20</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="C45" s="1">
+        <v>20</v>
+      </c>
+      <c r="D45" s="1">
+        <v>5</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I45" s="1">
+        <v>1</v>
+      </c>
+      <c r="S45" s="6"/>
+    </row>
+    <row r="46" ht="16.5" spans="1:19">
+      <c r="A46" s="1">
+        <v>141</v>
+      </c>
+      <c r="B46" s="5">
+        <v>30010007</v>
+      </c>
+      <c r="C46" s="1">
+        <v>20</v>
+      </c>
+      <c r="D46" s="1">
+        <v>5</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I46" s="1">
+        <v>1</v>
+      </c>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="6"/>
+      <c r="S46" s="6"/>
+    </row>
+    <row r="47" ht="16.5" spans="1:19">
+      <c r="A47" s="1">
+        <v>142</v>
+      </c>
+      <c r="B47" s="5">
+        <v>30010008</v>
+      </c>
+      <c r="C47" s="1">
+        <v>20</v>
+      </c>
+      <c r="D47" s="1">
+        <v>5</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I47" s="1">
+        <v>1</v>
+      </c>
+      <c r="L47" s="8"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="6"/>
+      <c r="S47" s="6"/>
+    </row>
+    <row r="48" ht="16.5" spans="1:19">
+      <c r="A48" s="1">
+        <v>143</v>
+      </c>
+      <c r="B48" s="5">
+        <v>30010009</v>
+      </c>
+      <c r="C48" s="1">
+        <v>20</v>
+      </c>
+      <c r="D48" s="1">
+        <v>5</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="8"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="6"/>
+      <c r="S48" s="6"/>
+    </row>
+    <row r="49" ht="16.5" spans="1:19">
+      <c r="A49" s="1">
+        <v>144</v>
+      </c>
+      <c r="B49" s="5">
+        <v>30010002</v>
+      </c>
+      <c r="C49" s="1">
+        <v>20</v>
+      </c>
+      <c r="D49" s="1">
+        <v>5</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="S7" s="7"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:19">
-      <c r="A8" s="2">
-        <v>103</v>
-      </c>
-      <c r="B8" s="6">
+      <c r="I49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="N49" s="6"/>
+      <c r="S49" s="6"/>
+    </row>
+    <row r="50" ht="16.5" spans="1:19">
+      <c r="A50" s="1">
+        <v>145</v>
+      </c>
+      <c r="B50" s="5">
+        <v>30010003</v>
+      </c>
+      <c r="C50" s="1">
+        <v>20</v>
+      </c>
+      <c r="D50" s="1">
+        <v>5</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="N50" s="6"/>
+      <c r="S50" s="6"/>
+    </row>
+    <row r="51" ht="16.5" spans="1:19">
+      <c r="A51" s="1">
+        <v>146</v>
+      </c>
+      <c r="B51" s="5">
+        <v>30010004</v>
+      </c>
+      <c r="C51" s="1">
+        <v>20</v>
+      </c>
+      <c r="D51" s="1">
+        <v>5</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="N51" s="6"/>
+      <c r="S51" s="6"/>
+    </row>
+    <row r="52" ht="16.5" spans="1:19">
+      <c r="A52" s="1">
+        <v>147</v>
+      </c>
+      <c r="B52" s="5">
+        <v>30010005</v>
+      </c>
+      <c r="C52" s="1">
+        <v>20</v>
+      </c>
+      <c r="D52" s="1">
+        <v>5</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="N52" s="6"/>
+      <c r="S52" s="6"/>
+    </row>
+    <row r="53" ht="16.5" spans="1:19">
+      <c r="A53" s="1">
+        <v>148</v>
+      </c>
+      <c r="B53" s="5">
+        <v>30010006</v>
+      </c>
+      <c r="C53" s="1">
+        <v>20</v>
+      </c>
+      <c r="D53" s="1">
+        <v>5</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I53" s="1">
+        <v>1</v>
+      </c>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="N53" s="6"/>
+      <c r="S53" s="6"/>
+    </row>
+    <row r="54" ht="16.5" spans="1:19">
+      <c r="A54" s="1">
+        <v>149</v>
+      </c>
+      <c r="B54" s="5">
+        <v>30010007</v>
+      </c>
+      <c r="C54" s="1">
+        <v>20</v>
+      </c>
+      <c r="D54" s="1">
+        <v>5</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="N54" s="6"/>
+      <c r="S54" s="6"/>
+    </row>
+    <row r="55" ht="16.5" spans="1:19">
+      <c r="A55" s="1">
+        <v>150</v>
+      </c>
+      <c r="B55" s="5">
+        <v>30010008</v>
+      </c>
+      <c r="C55" s="1">
+        <v>20</v>
+      </c>
+      <c r="D55" s="1">
+        <v>5</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I55" s="1">
+        <v>1</v>
+      </c>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="N55" s="6"/>
+      <c r="S55" s="6"/>
+    </row>
+    <row r="56" ht="16.5" spans="1:19">
+      <c r="A56" s="1">
+        <v>151</v>
+      </c>
+      <c r="B56" s="5">
+        <v>30010009</v>
+      </c>
+      <c r="C56" s="1">
+        <v>20</v>
+      </c>
+      <c r="D56" s="1">
+        <v>5</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I56" s="1">
+        <v>1</v>
+      </c>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="N56" s="6"/>
+      <c r="S56" s="6"/>
+    </row>
+    <row r="57" ht="16.5" spans="1:19">
+      <c r="A57" s="1">
+        <v>152</v>
+      </c>
+      <c r="B57" s="5">
         <v>30010012</v>
       </c>
-      <c r="C8" s="2">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="C57" s="1">
+        <v>20</v>
+      </c>
+      <c r="D57" s="1">
+        <v>5</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I57" s="1">
+        <v>2</v>
+      </c>
+      <c r="N57" s="6"/>
+      <c r="S57" s="6"/>
+    </row>
+    <row r="58" ht="16.5" spans="1:19">
+      <c r="A58" s="1">
+        <v>153</v>
+      </c>
+      <c r="B58" s="5">
+        <v>30010013</v>
+      </c>
+      <c r="C58" s="1">
+        <v>20</v>
+      </c>
+      <c r="D58" s="1">
+        <v>5</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I58" s="1">
+        <v>2</v>
+      </c>
+      <c r="N58" s="6"/>
+      <c r="S58" s="6"/>
+    </row>
+    <row r="59" ht="16.5" spans="1:19">
+      <c r="A59" s="1">
+        <v>154</v>
+      </c>
+      <c r="B59" s="5">
+        <v>30010014</v>
+      </c>
+      <c r="C59" s="1">
+        <v>20</v>
+      </c>
+      <c r="D59" s="1">
+        <v>5</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I59" s="1">
+        <v>2</v>
+      </c>
+      <c r="N59" s="6"/>
+      <c r="S59" s="6"/>
+    </row>
+    <row r="60" ht="16.5" spans="1:19">
+      <c r="A60" s="1">
+        <v>155</v>
+      </c>
+      <c r="B60" s="5">
+        <v>30010015</v>
+      </c>
+      <c r="C60" s="1">
+        <v>20</v>
+      </c>
+      <c r="D60" s="1">
+        <v>5</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I60" s="1">
+        <v>2</v>
+      </c>
+      <c r="N60" s="6"/>
+      <c r="S60" s="6"/>
+    </row>
+    <row r="61" ht="16.5" spans="1:19">
+      <c r="A61" s="1">
+        <v>156</v>
+      </c>
+      <c r="B61" s="5">
+        <v>30010015</v>
+      </c>
+      <c r="C61" s="1">
+        <v>20</v>
+      </c>
+      <c r="D61" s="1">
+        <v>5</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I61" s="1">
+        <v>2</v>
+      </c>
+      <c r="J61" s="7"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="7"/>
+      <c r="M61" s="7"/>
+      <c r="N61" s="6"/>
+      <c r="S61" s="6"/>
+    </row>
+    <row r="62" ht="16.5" spans="1:19">
+      <c r="A62" s="1">
+        <v>157</v>
+      </c>
+      <c r="B62" s="1">
+        <v>3000104</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="1">
+        <v>5</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F62" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="2">
-        <v>2</v>
-      </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="7"/>
-      <c r="S8" s="7"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:19">
-      <c r="A9" s="2">
-        <v>104</v>
-      </c>
-      <c r="B9" s="6">
-        <v>30010015</v>
-      </c>
-      <c r="C9" s="2">
-        <v>20</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="2">
-        <v>2</v>
-      </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="7"/>
-      <c r="S9" s="7"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:19">
-      <c r="A10" s="2">
-        <v>105</v>
-      </c>
-      <c r="B10" s="6">
-        <v>30010003</v>
-      </c>
-      <c r="C10" s="2">
-        <v>20</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:19">
-      <c r="A11" s="2">
-        <v>106</v>
-      </c>
-      <c r="B11" s="6">
-        <v>30010007</v>
-      </c>
-      <c r="C11" s="2">
-        <v>20</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="7"/>
-      <c r="S11" s="7"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:19">
-      <c r="A12" s="2">
-        <v>107</v>
-      </c>
-      <c r="B12" s="6">
-        <v>30010013</v>
-      </c>
-      <c r="C12" s="2">
-        <v>20</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="2">
-        <v>2</v>
-      </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="7"/>
-      <c r="S12" s="7"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:19">
-      <c r="A13" s="2">
-        <v>108</v>
-      </c>
-      <c r="B13" s="6">
-        <v>30010004</v>
-      </c>
-      <c r="C13" s="2">
-        <v>20</v>
-      </c>
-      <c r="D13" s="2">
-        <v>1</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:19">
-      <c r="A14" s="2">
-        <v>109</v>
-      </c>
-      <c r="B14" s="6">
-        <v>30010008</v>
-      </c>
-      <c r="C14" s="2">
-        <v>20</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="7"/>
-      <c r="S14" s="7"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:19">
-      <c r="A15" s="2">
-        <v>110</v>
-      </c>
-      <c r="B15" s="6">
-        <v>30010014</v>
-      </c>
-      <c r="C15" s="2">
-        <v>20</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I15" s="2">
-        <v>2</v>
-      </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="7"/>
-      <c r="S15" s="7"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:19">
-      <c r="A16" s="2">
-        <v>111</v>
-      </c>
-      <c r="B16" s="6">
-        <v>30010005</v>
-      </c>
-      <c r="C16" s="2">
-        <v>20</v>
-      </c>
-      <c r="D16" s="2">
-        <v>1</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="7"/>
-      <c r="S16" s="7"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:19">
-      <c r="A17" s="2">
-        <v>112</v>
-      </c>
-      <c r="B17" s="6">
-        <v>30010009</v>
-      </c>
-      <c r="C17" s="2">
-        <v>20</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I17" s="2">
-        <v>1</v>
-      </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="7"/>
-      <c r="S17" s="7"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:19">
-      <c r="A18" s="2">
-        <v>113</v>
-      </c>
-      <c r="B18" s="6">
-        <v>30010001</v>
-      </c>
-      <c r="C18" s="2">
-        <v>100</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="N18" s="7"/>
-      <c r="S18" s="7"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:19">
-      <c r="A19" s="2">
-        <v>114</v>
-      </c>
-      <c r="B19" s="6">
-        <v>30010002</v>
-      </c>
-      <c r="C19" s="2">
-        <v>100</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" s="2" t="s">
+      <c r="G62" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:19">
+      <c r="A63" s="1">
+        <v>158</v>
+      </c>
+      <c r="B63" s="14">
+        <v>60030067</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+      <c r="D63" s="1">
+        <v>5</v>
+      </c>
+      <c r="E63" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F63" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="N19" s="7"/>
-      <c r="S19" s="7"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:19">
-      <c r="A20" s="2">
-        <v>115</v>
-      </c>
-      <c r="B20" s="6">
-        <v>30010003</v>
-      </c>
-      <c r="C20" s="2">
-        <v>100</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="N20" s="7"/>
-      <c r="S20" s="7"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:19">
-      <c r="A21" s="2">
-        <v>116</v>
-      </c>
-      <c r="B21" s="6">
-        <v>30010004</v>
-      </c>
-      <c r="C21" s="2">
-        <v>100</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I21" s="2">
-        <v>1</v>
-      </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="N21" s="7"/>
-      <c r="S21" s="7"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:19">
-      <c r="A22" s="2">
-        <v>117</v>
-      </c>
-      <c r="B22" s="6">
-        <v>30010005</v>
-      </c>
-      <c r="C22" s="2">
-        <v>100</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="N22" s="7"/>
-      <c r="S22" s="7"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:19">
-      <c r="A23" s="2">
-        <v>118</v>
-      </c>
-      <c r="B23" s="6">
-        <v>30010006</v>
-      </c>
-      <c r="C23" s="2">
-        <v>100</v>
-      </c>
-      <c r="D23" s="2">
-        <v>1</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="N23" s="7"/>
-      <c r="S23" s="7"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:19">
-      <c r="A24" s="2">
-        <v>119</v>
-      </c>
-      <c r="B24" s="6">
-        <v>30010007</v>
-      </c>
-      <c r="C24" s="2">
-        <v>100</v>
-      </c>
-      <c r="D24" s="2">
-        <v>1</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I24" s="2">
-        <v>1</v>
-      </c>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="N24" s="7"/>
-      <c r="S24" s="7"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:19">
-      <c r="A25" s="2">
-        <v>120</v>
-      </c>
-      <c r="B25" s="6">
-        <v>30010008</v>
-      </c>
-      <c r="C25" s="2">
-        <v>100</v>
-      </c>
-      <c r="D25" s="2">
-        <v>1</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I25" s="2">
-        <v>1</v>
-      </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="N25" s="7"/>
-      <c r="S25" s="7"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:19">
-      <c r="A26" s="2">
-        <v>121</v>
-      </c>
-      <c r="B26" s="6">
-        <v>30010009</v>
-      </c>
-      <c r="C26" s="2">
-        <v>100</v>
-      </c>
-      <c r="D26" s="2">
-        <v>1</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1</v>
-      </c>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="N26" s="7"/>
-      <c r="S26" s="7"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:19">
-      <c r="A27" s="2">
-        <v>122</v>
-      </c>
-      <c r="B27" s="6">
-        <v>30010012</v>
-      </c>
-      <c r="C27" s="2">
-        <v>100</v>
-      </c>
-      <c r="D27" s="2">
-        <v>1</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="2">
-        <v>2</v>
-      </c>
-      <c r="N27" s="7"/>
-      <c r="S27" s="7"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:19">
-      <c r="A28" s="2">
-        <v>123</v>
-      </c>
-      <c r="B28" s="6">
-        <v>30010013</v>
-      </c>
-      <c r="C28" s="2">
-        <v>100</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H28" s="2" t="s">
+      <c r="G63" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I28" s="2">
-        <v>2</v>
-      </c>
-      <c r="N28" s="7"/>
-      <c r="S28" s="7"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:19">
-      <c r="A29" s="2">
-        <v>124</v>
-      </c>
-      <c r="B29" s="6">
-        <v>30010014</v>
-      </c>
-      <c r="C29" s="2">
-        <v>100</v>
-      </c>
-      <c r="D29" s="2">
-        <v>1</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I29" s="2">
-        <v>2</v>
-      </c>
-      <c r="N29" s="7"/>
-      <c r="S29" s="7"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:19">
-      <c r="A30" s="2">
-        <v>125</v>
-      </c>
-      <c r="B30" s="6">
-        <v>30010015</v>
-      </c>
-      <c r="C30" s="2">
-        <v>100</v>
-      </c>
-      <c r="D30" s="2">
-        <v>1</v>
-      </c>
-      <c r="E30" s="7" t="s">
+    </row>
+    <row r="64" ht="16.5" spans="1:19">
+      <c r="A64" s="1">
+        <v>159</v>
+      </c>
+      <c r="B64" s="14">
+        <v>60030072</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1">
+        <v>5</v>
+      </c>
+      <c r="E64" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I30" s="2">
-        <v>2</v>
-      </c>
-      <c r="N30" s="7"/>
-      <c r="S30" s="7"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:19">
-      <c r="A31" s="2">
-        <v>126</v>
-      </c>
-      <c r="B31" s="2">
-        <v>20410111</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N31" s="7"/>
-      <c r="S31" s="7"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:19">
-      <c r="A32" s="2">
-        <v>127</v>
-      </c>
-      <c r="B32" s="2">
-        <v>20610111</v>
-      </c>
-      <c r="C32" s="2">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2">
-        <v>2</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N32" s="7"/>
-      <c r="S32" s="7"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:19">
-      <c r="A33" s="2">
-        <v>128</v>
-      </c>
-      <c r="B33" s="2">
-        <v>20810111</v>
-      </c>
-      <c r="C33" s="2">
-        <v>1</v>
-      </c>
-      <c r="D33" s="2">
-        <v>2</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N33" s="7"/>
-      <c r="S33" s="7"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:19">
-      <c r="A34" s="2">
-        <v>129</v>
-      </c>
-      <c r="B34" s="2">
-        <v>20710111</v>
-      </c>
-      <c r="C34" s="2">
-        <v>1</v>
-      </c>
-      <c r="D34" s="2">
-        <v>2</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N34" s="7"/>
-      <c r="S34" s="7"/>
-    </row>
-    <row r="35" ht="16.5" spans="1:19">
-      <c r="A35" s="2">
-        <v>130</v>
-      </c>
-      <c r="B35" s="2">
-        <v>20910111</v>
-      </c>
-      <c r="C35" s="2">
-        <v>1</v>
-      </c>
-      <c r="D35" s="2">
-        <v>2</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N35" s="7"/>
-      <c r="S35" s="7"/>
-    </row>
-    <row r="36" ht="16.5" spans="1:19">
-      <c r="A36" s="2">
-        <v>131</v>
-      </c>
-      <c r="B36" s="2">
-        <v>20310111</v>
-      </c>
-      <c r="C36" s="2">
-        <v>1</v>
-      </c>
-      <c r="D36" s="2">
-        <v>2</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N36" s="7"/>
-      <c r="S36" s="7"/>
-    </row>
-    <row r="37" ht="16.5" spans="1:19">
-      <c r="A37" s="2">
-        <v>132</v>
-      </c>
-      <c r="B37" s="2">
-        <v>60030032</v>
-      </c>
-      <c r="C37" s="2">
-        <v>1</v>
-      </c>
-      <c r="D37" s="2">
-        <v>2</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N37" s="7"/>
-      <c r="S37" s="7"/>
-    </row>
-    <row r="38" ht="16.5" spans="1:19">
-      <c r="A38" s="2">
-        <v>133</v>
-      </c>
-      <c r="B38" s="2">
-        <v>60030022</v>
-      </c>
-      <c r="C38" s="2">
-        <v>1</v>
-      </c>
-      <c r="D38" s="2">
-        <v>2</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N38" s="7"/>
-      <c r="S38" s="7"/>
-    </row>
-    <row r="39" ht="16.5" spans="1:19">
-      <c r="A39" s="2">
-        <v>134</v>
-      </c>
-      <c r="B39" s="2">
-        <v>60035068</v>
-      </c>
-      <c r="C39" s="2">
-        <v>1</v>
-      </c>
-      <c r="D39" s="2">
-        <v>2</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N39" s="7"/>
-      <c r="S39" s="7"/>
-    </row>
-    <row r="40" ht="16.5" spans="1:19">
-      <c r="A40" s="2">
-        <v>135</v>
-      </c>
-      <c r="B40" s="2">
-        <v>60030004</v>
-      </c>
-      <c r="C40" s="2">
-        <v>1</v>
-      </c>
-      <c r="D40" s="2">
-        <v>3</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F40" s="7"/>
-      <c r="H40" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="N40" s="7"/>
-      <c r="S40" s="7"/>
-    </row>
-    <row r="41" ht="16.5" spans="1:19">
-      <c r="A41" s="2">
-        <v>136</v>
-      </c>
-      <c r="B41" s="2">
-        <v>60030011</v>
-      </c>
-      <c r="C41" s="2">
-        <v>1</v>
-      </c>
-      <c r="D41" s="2">
-        <v>3</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F41" s="7"/>
-      <c r="H41" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N41" s="7"/>
-      <c r="S41" s="7"/>
-    </row>
-    <row r="42" ht="16.5" spans="1:19">
-      <c r="A42" s="2">
-        <v>137</v>
-      </c>
-      <c r="B42" s="2">
-        <v>60030003</v>
-      </c>
-      <c r="C42" s="2">
-        <v>1</v>
-      </c>
-      <c r="D42" s="2">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F42" s="7"/>
-      <c r="H42" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="N42" s="7"/>
-      <c r="S42" s="7"/>
-    </row>
-    <row r="43" ht="16.5" spans="1:19">
-      <c r="A43" s="2">
-        <v>138</v>
-      </c>
-      <c r="B43" s="2">
-        <v>60030006</v>
-      </c>
-      <c r="C43" s="2">
-        <v>1</v>
-      </c>
-      <c r="D43" s="2">
-        <v>3</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F43" s="7"/>
-      <c r="H43" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="N43" s="7"/>
-      <c r="S43" s="7"/>
-    </row>
-    <row r="44" ht="16.5" spans="1:19">
-      <c r="A44" s="2">
-        <v>139</v>
-      </c>
-      <c r="B44" s="2">
-        <v>60030002</v>
-      </c>
-      <c r="C44" s="2">
-        <v>1</v>
-      </c>
-      <c r="D44" s="2">
-        <v>3</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F44" s="7"/>
-      <c r="H44" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="45" ht="16.5" spans="1:19">
-      <c r="A45" s="2">
-        <v>140</v>
-      </c>
-      <c r="B45" s="2">
-        <v>60030007</v>
-      </c>
-      <c r="C45" s="2">
-        <v>1</v>
-      </c>
-      <c r="D45" s="2">
-        <v>3</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F45" s="7"/>
-      <c r="H45" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19">
-      <c r="A46" s="2">
-        <v>141</v>
-      </c>
-      <c r="B46" s="2">
-        <v>60030005</v>
-      </c>
-      <c r="C46" s="2">
-        <v>1</v>
-      </c>
-      <c r="D46" s="2">
-        <v>3</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="47" ht="16.5" spans="1:19">
-      <c r="A47" s="2">
-        <v>142</v>
-      </c>
-      <c r="B47" s="2">
-        <v>60030008</v>
-      </c>
-      <c r="C47" s="2">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F47" s="7"/>
-      <c r="H47" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:19">
-      <c r="A48" s="2">
-        <v>143</v>
-      </c>
-      <c r="B48" s="12">
-        <v>60030030</v>
-      </c>
-      <c r="C48" s="2">
-        <v>1</v>
-      </c>
-      <c r="D48" s="2">
-        <v>4</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="F48" s="7"/>
-      <c r="H48" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" ht="16.5" spans="1:19">
-      <c r="A49" s="2">
-        <v>144</v>
-      </c>
-      <c r="B49" s="12">
-        <v>60030031</v>
-      </c>
-      <c r="C49" s="2">
-        <v>1</v>
-      </c>
-      <c r="D49" s="2">
-        <v>4</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="F49" s="7"/>
-      <c r="H49" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" ht="16.5" spans="1:19">
-      <c r="A50" s="2">
-        <v>145</v>
-      </c>
-      <c r="B50" s="12">
-        <v>60030032</v>
-      </c>
-      <c r="C50" s="2">
-        <v>1</v>
-      </c>
-      <c r="D50" s="2">
-        <v>4</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="F50" s="7"/>
-      <c r="H50" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" ht="16.5" spans="1:19">
-      <c r="A51" s="2">
-        <v>146</v>
-      </c>
-      <c r="B51" s="12">
-        <v>60030033</v>
-      </c>
-      <c r="C51" s="2">
-        <v>1</v>
-      </c>
-      <c r="D51" s="2">
-        <v>4</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="F51" s="7"/>
-      <c r="H51" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" ht="16.5" spans="1:19">
-      <c r="A52" s="2">
-        <v>147</v>
-      </c>
-      <c r="B52" s="12">
-        <v>60030034</v>
-      </c>
-      <c r="C52" s="2">
-        <v>1</v>
-      </c>
-      <c r="D52" s="2">
-        <v>4</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F52" s="7"/>
-      <c r="H52" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="53" ht="16.5" spans="1:19">
-      <c r="A53" s="2">
-        <v>148</v>
-      </c>
-      <c r="B53" s="2">
-        <v>3000104</v>
-      </c>
-      <c r="C53" s="2">
-        <v>1</v>
-      </c>
-      <c r="D53" s="2">
+      <c r="F64" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" s="13" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A65" s="1">
+        <v>160</v>
+      </c>
+      <c r="B65" s="14">
+        <v>60030072</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1</v>
+      </c>
+      <c r="D65" s="1">
         <v>5</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" ht="16.5" spans="1:19">
-      <c r="A54" s="2">
-        <v>149</v>
-      </c>
-      <c r="B54" s="6">
-        <v>30010001</v>
-      </c>
-      <c r="C54" s="2">
-        <v>20</v>
-      </c>
-      <c r="D54" s="2">
-        <v>5</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I54" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" ht="16.5" spans="1:19">
-      <c r="A55" s="2">
-        <v>150</v>
-      </c>
-      <c r="B55" s="6">
-        <v>30010002</v>
-      </c>
-      <c r="C55" s="2">
-        <v>20</v>
-      </c>
-      <c r="D55" s="2">
-        <v>5</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H55" s="2" t="s">
+      <c r="E65" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F65" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I55" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" ht="16.5" spans="1:19">
-      <c r="A56" s="2">
-        <v>151</v>
-      </c>
-      <c r="B56" s="6">
-        <v>30010006</v>
-      </c>
-      <c r="C56" s="2">
-        <v>20</v>
-      </c>
-      <c r="D56" s="2">
-        <v>5</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I56" s="2">
-        <v>1</v>
-      </c>
-      <c r="S56" s="7"/>
-    </row>
-    <row r="57" ht="16.5" spans="1:19">
-      <c r="A57" s="2">
-        <v>152</v>
-      </c>
-      <c r="B57" s="6">
-        <v>30010012</v>
-      </c>
-      <c r="C57" s="2">
-        <v>20</v>
-      </c>
-      <c r="D57" s="2">
-        <v>5</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I57" s="2">
-        <v>2</v>
-      </c>
-      <c r="J57" s="8"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="8"/>
-      <c r="N57" s="7"/>
-      <c r="S57" s="7"/>
-    </row>
-    <row r="58" ht="16.5" spans="1:19">
-      <c r="A58" s="2">
-        <v>153</v>
-      </c>
-      <c r="B58" s="6">
-        <v>30010015</v>
-      </c>
-      <c r="C58" s="2">
-        <v>20</v>
-      </c>
-      <c r="D58" s="2">
-        <v>5</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I58" s="2">
-        <v>2</v>
-      </c>
-      <c r="J58" s="8"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="8"/>
-      <c r="N58" s="7"/>
-      <c r="S58" s="7"/>
-    </row>
-    <row r="59" ht="16.5" spans="1:19">
-      <c r="A59" s="2">
-        <v>154</v>
-      </c>
-      <c r="B59" s="6">
-        <v>30010003</v>
-      </c>
-      <c r="C59" s="2">
-        <v>20</v>
-      </c>
-      <c r="D59" s="2">
-        <v>5</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I59" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" ht="16.5" spans="1:19">
-      <c r="A60" s="2">
-        <v>155</v>
-      </c>
-      <c r="B60" s="6">
-        <v>30010007</v>
-      </c>
-      <c r="C60" s="2">
-        <v>20</v>
-      </c>
-      <c r="D60" s="2">
-        <v>5</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I60" s="2">
-        <v>1</v>
-      </c>
-      <c r="L60" s="9"/>
-      <c r="M60" s="9"/>
-      <c r="N60" s="7"/>
-      <c r="S60" s="7"/>
-    </row>
-    <row r="61" ht="16.5" spans="1:19">
-      <c r="A61" s="2">
-        <v>156</v>
-      </c>
-      <c r="B61" s="6">
-        <v>30010013</v>
-      </c>
-      <c r="C61" s="2">
-        <v>20</v>
-      </c>
-      <c r="D61" s="2">
-        <v>5</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I61" s="2">
-        <v>2</v>
-      </c>
-      <c r="J61" s="8"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="8"/>
-      <c r="M61" s="8"/>
-      <c r="N61" s="7"/>
-      <c r="S61" s="7"/>
-    </row>
-    <row r="62" ht="16.5" spans="1:19">
-      <c r="A62" s="2">
-        <v>157</v>
-      </c>
-      <c r="B62" s="6">
-        <v>30010004</v>
-      </c>
-      <c r="C62" s="2">
-        <v>20</v>
-      </c>
-      <c r="D62" s="2">
-        <v>5</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I62" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:19">
-      <c r="A63" s="2">
-        <v>158</v>
-      </c>
-      <c r="B63" s="6">
-        <v>30010008</v>
-      </c>
-      <c r="C63" s="2">
-        <v>20</v>
-      </c>
-      <c r="D63" s="2">
-        <v>5</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I63" s="2">
-        <v>1</v>
-      </c>
-      <c r="L63" s="9"/>
-      <c r="M63" s="8"/>
-      <c r="N63" s="7"/>
-      <c r="S63" s="7"/>
-    </row>
-    <row r="64" ht="16.5" spans="1:19">
-      <c r="A64" s="2">
-        <v>159</v>
-      </c>
-      <c r="B64" s="6">
-        <v>30010014</v>
-      </c>
-      <c r="C64" s="2">
-        <v>20</v>
-      </c>
-      <c r="D64" s="2">
-        <v>5</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I64" s="2">
-        <v>2</v>
-      </c>
-      <c r="J64" s="8"/>
-      <c r="K64" s="9"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="8"/>
-      <c r="N64" s="7"/>
-      <c r="S64" s="7"/>
-    </row>
-    <row r="65" ht="16.5" spans="1:19">
-      <c r="A65" s="2">
-        <v>160</v>
-      </c>
-      <c r="B65" s="6">
-        <v>30010005</v>
-      </c>
-      <c r="C65" s="2">
-        <v>20</v>
-      </c>
-      <c r="D65" s="2">
-        <v>5</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I65" s="2">
-        <v>1</v>
-      </c>
-      <c r="M65" s="9"/>
-      <c r="N65" s="7"/>
-      <c r="S65" s="7"/>
-    </row>
-    <row r="66" ht="16.5" spans="1:19">
-      <c r="A66" s="2">
-        <v>161</v>
-      </c>
-      <c r="B66" s="6">
-        <v>30010009</v>
-      </c>
-      <c r="C66" s="2">
-        <v>20</v>
-      </c>
-      <c r="D66" s="2">
-        <v>5</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I66" s="2">
-        <v>1</v>
-      </c>
-      <c r="K66" s="9"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="8"/>
-      <c r="N66" s="7"/>
-      <c r="S66" s="7"/>
-    </row>
-    <row r="67" ht="16.5" spans="1:19">
-      <c r="A67" s="2">
-        <v>162</v>
-      </c>
-      <c r="B67" s="6">
-        <v>30010001</v>
-      </c>
-      <c r="C67" s="2">
-        <v>100</v>
-      </c>
-      <c r="D67" s="2">
-        <v>5</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I67" s="2">
-        <v>1</v>
-      </c>
-      <c r="K67" s="9"/>
-      <c r="L67" s="9"/>
-      <c r="N67" s="7"/>
-      <c r="S67" s="7"/>
-    </row>
-    <row r="68" ht="16.5" spans="1:19">
-      <c r="A68" s="2">
-        <v>163</v>
-      </c>
-      <c r="B68" s="6">
-        <v>30010002</v>
-      </c>
-      <c r="C68" s="2">
-        <v>100</v>
-      </c>
-      <c r="D68" s="2">
-        <v>5</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I68" s="2">
-        <v>1</v>
-      </c>
-      <c r="K68" s="9"/>
-      <c r="L68" s="9"/>
-      <c r="N68" s="7"/>
-      <c r="S68" s="7"/>
-    </row>
-    <row r="69" ht="16.5" spans="1:19">
-      <c r="A69" s="2">
-        <v>164</v>
-      </c>
-      <c r="B69" s="6">
-        <v>30010003</v>
-      </c>
-      <c r="C69" s="2">
-        <v>100</v>
-      </c>
-      <c r="D69" s="2">
-        <v>5</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I69" s="2">
-        <v>1</v>
-      </c>
-      <c r="K69" s="9"/>
-      <c r="L69" s="9"/>
-      <c r="N69" s="7"/>
-      <c r="S69" s="7"/>
-    </row>
-    <row r="70" ht="16.5" spans="1:19">
-      <c r="A70" s="2">
-        <v>165</v>
-      </c>
-      <c r="B70" s="6">
-        <v>30010004</v>
-      </c>
-      <c r="C70" s="2">
-        <v>100</v>
-      </c>
-      <c r="D70" s="2">
-        <v>5</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I70" s="2">
-        <v>1</v>
-      </c>
-      <c r="K70" s="9"/>
-      <c r="L70" s="9"/>
-      <c r="N70" s="7"/>
-      <c r="S70" s="7"/>
-    </row>
-    <row r="71" ht="16.5" spans="1:19">
-      <c r="A71" s="2">
-        <v>166</v>
-      </c>
-      <c r="B71" s="6">
-        <v>30010005</v>
-      </c>
-      <c r="C71" s="2">
-        <v>100</v>
-      </c>
-      <c r="D71" s="2">
-        <v>5</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I71" s="2">
-        <v>1</v>
-      </c>
-      <c r="K71" s="9"/>
-      <c r="L71" s="9"/>
-      <c r="N71" s="7"/>
-      <c r="S71" s="7"/>
-    </row>
-    <row r="72" ht="16.5" spans="1:19">
-      <c r="A72" s="2">
-        <v>167</v>
-      </c>
-      <c r="B72" s="6">
-        <v>30010006</v>
-      </c>
-      <c r="C72" s="2">
-        <v>100</v>
-      </c>
-      <c r="D72" s="2">
-        <v>5</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I72" s="2">
-        <v>1</v>
-      </c>
-      <c r="K72" s="9"/>
-      <c r="L72" s="9"/>
-      <c r="N72" s="7"/>
-      <c r="S72" s="7"/>
-    </row>
-    <row r="73" ht="16.5" spans="1:19">
-      <c r="A73" s="2">
-        <v>168</v>
-      </c>
-      <c r="B73" s="6">
-        <v>30010007</v>
-      </c>
-      <c r="C73" s="2">
-        <v>100</v>
-      </c>
-      <c r="D73" s="2">
-        <v>5</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I73" s="2">
-        <v>1</v>
-      </c>
-      <c r="K73" s="9"/>
-      <c r="L73" s="9"/>
-      <c r="N73" s="7"/>
-      <c r="S73" s="7"/>
-    </row>
-    <row r="74" ht="16.5" spans="1:19">
-      <c r="A74" s="2">
-        <v>169</v>
-      </c>
-      <c r="B74" s="6">
-        <v>30010008</v>
-      </c>
-      <c r="C74" s="2">
-        <v>100</v>
-      </c>
-      <c r="D74" s="2">
-        <v>5</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I74" s="2">
-        <v>1</v>
-      </c>
-      <c r="K74" s="9"/>
-      <c r="L74" s="9"/>
-      <c r="N74" s="7"/>
-      <c r="S74" s="7"/>
-    </row>
-    <row r="75" ht="16.5" spans="1:19">
-      <c r="A75" s="2">
-        <v>170</v>
-      </c>
-      <c r="B75" s="6">
-        <v>30010009</v>
-      </c>
-      <c r="C75" s="2">
-        <v>100</v>
-      </c>
-      <c r="D75" s="2">
-        <v>5</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I75" s="2">
-        <v>1</v>
-      </c>
-      <c r="K75" s="9"/>
-      <c r="L75" s="9"/>
-      <c r="N75" s="7"/>
-      <c r="S75" s="7"/>
-    </row>
-    <row r="76" ht="16.5" spans="1:19">
-      <c r="A76" s="2">
-        <v>171</v>
-      </c>
-      <c r="B76" s="6">
-        <v>30010012</v>
-      </c>
-      <c r="C76" s="2">
-        <v>100</v>
-      </c>
-      <c r="D76" s="2">
-        <v>5</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I76" s="2">
-        <v>2</v>
-      </c>
-      <c r="N76" s="7"/>
-      <c r="S76" s="7"/>
-    </row>
-    <row r="77" ht="16.5" spans="1:19">
-      <c r="A77" s="2">
-        <v>172</v>
-      </c>
-      <c r="B77" s="6">
-        <v>30010013</v>
-      </c>
-      <c r="C77" s="2">
-        <v>100</v>
-      </c>
-      <c r="D77" s="2">
-        <v>5</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H77" s="2" t="s">
+      <c r="G65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I77" s="2">
-        <v>2</v>
-      </c>
-      <c r="N77" s="7"/>
-      <c r="S77" s="7"/>
-    </row>
-    <row r="78" ht="16.5" spans="1:19">
-      <c r="A78" s="2">
-        <v>173</v>
-      </c>
-      <c r="B78" s="6">
-        <v>30010014</v>
-      </c>
-      <c r="C78" s="2">
-        <v>100</v>
-      </c>
-      <c r="D78" s="2">
-        <v>5</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I78" s="2">
-        <v>2</v>
-      </c>
-      <c r="N78" s="7"/>
-      <c r="S78" s="7"/>
-    </row>
-    <row r="79" ht="16.5" spans="1:19">
-      <c r="A79" s="2">
-        <v>174</v>
-      </c>
-      <c r="B79" s="6">
-        <v>30010015</v>
-      </c>
-      <c r="C79" s="2">
-        <v>100</v>
-      </c>
-      <c r="D79" s="2">
-        <v>5</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I79" s="2">
-        <v>2</v>
-      </c>
-      <c r="N79" s="7"/>
-      <c r="S79" s="7"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M43">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="24"/>
+  <conditionalFormatting sqref="M31">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A$1:A$1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="26"/>
+  <conditionalFormatting sqref="B33">
+    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48:B49">
-    <cfRule type="duplicateValues" dxfId="1" priority="22"/>
-    <cfRule type="cellIs" dxfId="2" priority="17" operator="greaterThan">
-      <formula>2147483647</formula>
-    </cfRule>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50:B52">
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="greaterThan">
-      <formula>2147483647</formula>
-    </cfRule>
+  <conditionalFormatting sqref="M34">
+    <cfRule type="duplicateValues" dxfId="1" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M44:M52">
-    <cfRule type="duplicateValues" dxfId="1" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
+  <conditionalFormatting sqref="M61">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M18:M26 M15 M8:M9 M12">
-    <cfRule type="duplicateValues" dxfId="1" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M11 M14 M16:M17 M27:M42">
-    <cfRule type="duplicateValues" dxfId="1" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+  <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M57:M58 M61 M64 M67:M75">
-    <cfRule type="duplicateValues" dxfId="1" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  <conditionalFormatting sqref="M64">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M60 M63 M65:M66 M76:M79">
-    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  <conditionalFormatting sqref="A65">
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B65">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M65">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A64 A66:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M6 M11:M14 M19:M26">
+    <cfRule type="duplicateValues" dxfId="1" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="150"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M10 M16:M18 M27:M30 M33">
+    <cfRule type="duplicateValues" dxfId="1" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="152"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M36 M41:M44 M49:M56">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M40 M46:M48 M57:M60 M63">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4487,7 +4256,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1">
+      <c r="A1" s="12">
         <v>30010001</v>
       </c>
       <c r="B1">
@@ -4495,7 +4264,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1">
+      <c r="A2" s="12">
         <v>30010002</v>
       </c>
       <c r="B2">
@@ -4503,7 +4272,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="1">
+      <c r="A3" s="12">
         <v>30010003</v>
       </c>
       <c r="B3">
@@ -4511,7 +4280,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="1">
+      <c r="A4" s="12">
         <v>30010004</v>
       </c>
       <c r="B4">
@@ -4519,7 +4288,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="1">
+      <c r="A5" s="12">
         <v>30010005</v>
       </c>
       <c r="B5">
@@ -4527,7 +4296,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="1">
+      <c r="A6" s="12">
         <v>30010006</v>
       </c>
       <c r="B6">
@@ -4535,7 +4304,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="1">
+      <c r="A7" s="12">
         <v>30010007</v>
       </c>
       <c r="B7">
@@ -4543,7 +4312,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="1">
+      <c r="A8" s="12">
         <v>30010008</v>
       </c>
       <c r="B8">
@@ -4551,7 +4320,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="1">
+      <c r="A9" s="12">
         <v>30010009</v>
       </c>
       <c r="B9">
@@ -4559,7 +4328,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="1">
+      <c r="A10" s="12">
         <v>30010010</v>
       </c>
       <c r="B10">
@@ -4567,7 +4336,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="1">
+      <c r="A11" s="12">
         <v>30010011</v>
       </c>
       <c r="B11">
@@ -4575,7 +4344,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="1">
+      <c r="A12" s="12">
         <v>30010012</v>
       </c>
       <c r="B12">
@@ -4583,7 +4352,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="1">
+      <c r="A13" s="12">
         <v>30010013</v>
       </c>
       <c r="B13">
@@ -4591,7 +4360,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="1">
+      <c r="A14" s="12">
         <v>30010014</v>
       </c>
       <c r="B14">
@@ -4599,7 +4368,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="1">
+      <c r="A15" s="12">
         <v>30010015</v>
       </c>
       <c r="B15">
@@ -4607,7 +4376,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="1">
+      <c r="A16" s="12">
         <v>30010016</v>
       </c>
       <c r="B16">
@@ -4615,7 +4384,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="1">
+      <c r="A17" s="12">
         <v>30010017</v>
       </c>
       <c r="B17">
@@ -4623,7 +4392,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="1">
+      <c r="A18" s="12">
         <v>30010018</v>
       </c>
       <c r="B18">
@@ -4631,7 +4400,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="1">
+      <c r="A19" s="12">
         <v>30010019</v>
       </c>
       <c r="B19">
@@ -4639,7 +4408,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="1">
+      <c r="A20" s="12">
         <v>30010020</v>
       </c>
       <c r="B20">
@@ -4647,7 +4416,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="1">
+      <c r="A21" s="12">
         <v>30010021</v>
       </c>
       <c r="B21">
@@ -4655,7 +4424,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="1">
+      <c r="A22" s="12">
         <v>30010022</v>
       </c>
       <c r="B22">
@@ -4663,7 +4432,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="1">
+      <c r="A23" s="12">
         <v>30010001</v>
       </c>
       <c r="B23">
@@ -4671,7 +4440,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="1">
+      <c r="A24" s="12">
         <v>30010002</v>
       </c>
       <c r="B24">
@@ -4679,7 +4448,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="1">
+      <c r="A25" s="12">
         <v>30010003</v>
       </c>
       <c r="B25">
@@ -4687,7 +4456,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="1">
+      <c r="A26" s="12">
         <v>30010004</v>
       </c>
       <c r="B26">
@@ -4695,7 +4464,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="1">
+      <c r="A27" s="12">
         <v>30010005</v>
       </c>
       <c r="B27">
@@ -4703,7 +4472,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="1">
+      <c r="A28" s="12">
         <v>30010006</v>
       </c>
       <c r="B28">
@@ -4711,7 +4480,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="1">
+      <c r="A29" s="12">
         <v>30010007</v>
       </c>
       <c r="B29">
@@ -4719,7 +4488,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="1">
+      <c r="A30" s="12">
         <v>30010008</v>
       </c>
       <c r="B30">
@@ -4727,7 +4496,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="1">
+      <c r="A31" s="12">
         <v>30010009</v>
       </c>
       <c r="B31">
@@ -4735,7 +4504,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="1">
+      <c r="A32" s="12">
         <v>30010010</v>
       </c>
       <c r="B32">
@@ -4743,7 +4512,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="1">
+      <c r="A33" s="12">
         <v>30010011</v>
       </c>
       <c r="B33">
@@ -4751,7 +4520,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="1">
+      <c r="A34" s="12">
         <v>30010012</v>
       </c>
       <c r="B34">
@@ -4759,7 +4528,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="1">
+      <c r="A35" s="12">
         <v>30010013</v>
       </c>
       <c r="B35">
@@ -4767,7 +4536,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="1">
+      <c r="A36" s="12">
         <v>30010014</v>
       </c>
       <c r="B36">
@@ -4775,7 +4544,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="1">
+      <c r="A37" s="12">
         <v>30010015</v>
       </c>
       <c r="B37">
@@ -4783,7 +4552,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="1">
+      <c r="A38" s="12">
         <v>30010016</v>
       </c>
       <c r="B38">
@@ -4791,7 +4560,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="1">
+      <c r="A39" s="12">
         <v>30010017</v>
       </c>
       <c r="B39">
@@ -4799,7 +4568,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="1">
+      <c r="A40" s="12">
         <v>30010018</v>
       </c>
       <c r="B40">
@@ -4807,7 +4576,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="1">
+      <c r="A41" s="12">
         <v>30010019</v>
       </c>
       <c r="B41">
@@ -4815,7 +4584,7 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="1">
+      <c r="A42" s="12">
         <v>30010020</v>
       </c>
       <c r="B42">
@@ -4823,7 +4592,7 @@
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="1">
+      <c r="A43" s="12">
         <v>30010021</v>
       </c>
       <c r="B43">
@@ -4831,7 +4600,7 @@
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="1">
+      <c r="A44" s="12">
         <v>30010022</v>
       </c>
       <c r="B44">
@@ -5387,4 +5156,2395 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:S79"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="31.2857142857143" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.1428571428571" style="1" customWidth="1"/>
+    <col min="4" max="4" width="65.1428571428571" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24" style="1" customWidth="1"/>
+    <col min="6" max="6" width="45.7142857142857" style="1" customWidth="1"/>
+    <col min="7" max="7" width="54.4285714285714" style="1" customWidth="1"/>
+    <col min="8" max="8" width="41" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.8571428571429" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1"/>
+    <col min="11" max="12" width="10.5714285714286" style="1"/>
+    <col min="13" max="13" width="9.57142857142857" style="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:19">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:19">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:19">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:19">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A5" s="1">
+        <v>100</v>
+      </c>
+      <c r="B5" s="5">
+        <v>30010001</v>
+      </c>
+      <c r="C5" s="1">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A6" s="1">
+        <v>101</v>
+      </c>
+      <c r="B6" s="5">
+        <v>30010002</v>
+      </c>
+      <c r="C6" s="1">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A7" s="1">
+        <v>102</v>
+      </c>
+      <c r="B7" s="5">
+        <v>30010006</v>
+      </c>
+      <c r="C7" s="1">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="S7" s="6"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A8" s="1">
+        <v>103</v>
+      </c>
+      <c r="B8" s="5">
+        <v>30010012</v>
+      </c>
+      <c r="C8" s="1">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2</v>
+      </c>
+      <c r="J8" s="7"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="6"/>
+      <c r="S8" s="6"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A9" s="1">
+        <v>104</v>
+      </c>
+      <c r="B9" s="5">
+        <v>30010015</v>
+      </c>
+      <c r="C9" s="1">
+        <v>20</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2</v>
+      </c>
+      <c r="J9" s="7"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="6"/>
+      <c r="S9" s="6"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A10" s="1">
+        <v>105</v>
+      </c>
+      <c r="B10" s="5">
+        <v>30010003</v>
+      </c>
+      <c r="C10" s="1">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A11" s="1">
+        <v>106</v>
+      </c>
+      <c r="B11" s="5">
+        <v>30010007</v>
+      </c>
+      <c r="C11" s="1">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="6"/>
+      <c r="S11" s="6"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A12" s="1">
+        <v>107</v>
+      </c>
+      <c r="B12" s="5">
+        <v>30010013</v>
+      </c>
+      <c r="C12" s="1">
+        <v>20</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="6"/>
+      <c r="S12" s="6"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A13" s="1">
+        <v>108</v>
+      </c>
+      <c r="B13" s="5">
+        <v>30010004</v>
+      </c>
+      <c r="C13" s="1">
+        <v>20</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A14" s="1">
+        <v>109</v>
+      </c>
+      <c r="B14" s="5">
+        <v>30010008</v>
+      </c>
+      <c r="C14" s="1">
+        <v>20</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="8"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="6"/>
+      <c r="S14" s="6"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A15" s="1">
+        <v>110</v>
+      </c>
+      <c r="B15" s="5">
+        <v>30010014</v>
+      </c>
+      <c r="C15" s="1">
+        <v>20</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2</v>
+      </c>
+      <c r="J15" s="7"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="6"/>
+      <c r="S15" s="6"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A16" s="1">
+        <v>111</v>
+      </c>
+      <c r="B16" s="5">
+        <v>30010005</v>
+      </c>
+      <c r="C16" s="1">
+        <v>20</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="M16" s="8"/>
+      <c r="N16" s="6"/>
+      <c r="S16" s="6"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A17" s="1">
+        <v>112</v>
+      </c>
+      <c r="B17" s="5">
+        <v>30010009</v>
+      </c>
+      <c r="C17" s="1">
+        <v>20</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="8"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="6"/>
+      <c r="S17" s="6"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A18" s="1">
+        <v>113</v>
+      </c>
+      <c r="B18" s="5">
+        <v>30010001</v>
+      </c>
+      <c r="C18" s="1">
+        <v>100</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="N18" s="6"/>
+      <c r="S18" s="6"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A19" s="1">
+        <v>114</v>
+      </c>
+      <c r="B19" s="5">
+        <v>30010002</v>
+      </c>
+      <c r="C19" s="1">
+        <v>100</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="N19" s="6"/>
+      <c r="S19" s="6"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A20" s="1">
+        <v>115</v>
+      </c>
+      <c r="B20" s="5">
+        <v>30010003</v>
+      </c>
+      <c r="C20" s="1">
+        <v>100</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="N20" s="6"/>
+      <c r="S20" s="6"/>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A21" s="1">
+        <v>116</v>
+      </c>
+      <c r="B21" s="5">
+        <v>30010004</v>
+      </c>
+      <c r="C21" s="1">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="N21" s="6"/>
+      <c r="S21" s="6"/>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A22" s="1">
+        <v>117</v>
+      </c>
+      <c r="B22" s="5">
+        <v>30010005</v>
+      </c>
+      <c r="C22" s="1">
+        <v>100</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="N22" s="6"/>
+      <c r="S22" s="6"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A23" s="1">
+        <v>118</v>
+      </c>
+      <c r="B23" s="5">
+        <v>30010006</v>
+      </c>
+      <c r="C23" s="1">
+        <v>100</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="N23" s="6"/>
+      <c r="S23" s="6"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A24" s="1">
+        <v>119</v>
+      </c>
+      <c r="B24" s="5">
+        <v>30010007</v>
+      </c>
+      <c r="C24" s="1">
+        <v>100</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="N24" s="6"/>
+      <c r="S24" s="6"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A25" s="1">
+        <v>120</v>
+      </c>
+      <c r="B25" s="5">
+        <v>30010008</v>
+      </c>
+      <c r="C25" s="1">
+        <v>100</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="N25" s="6"/>
+      <c r="S25" s="6"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A26" s="1">
+        <v>121</v>
+      </c>
+      <c r="B26" s="5">
+        <v>30010009</v>
+      </c>
+      <c r="C26" s="1">
+        <v>100</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="N26" s="6"/>
+      <c r="S26" s="6"/>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A27" s="1">
+        <v>122</v>
+      </c>
+      <c r="B27" s="5">
+        <v>30010012</v>
+      </c>
+      <c r="C27" s="1">
+        <v>100</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2</v>
+      </c>
+      <c r="N27" s="6"/>
+      <c r="S27" s="6"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A28" s="1">
+        <v>123</v>
+      </c>
+      <c r="B28" s="5">
+        <v>30010013</v>
+      </c>
+      <c r="C28" s="1">
+        <v>100</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28" s="1">
+        <v>2</v>
+      </c>
+      <c r="N28" s="6"/>
+      <c r="S28" s="6"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A29" s="1">
+        <v>124</v>
+      </c>
+      <c r="B29" s="5">
+        <v>30010014</v>
+      </c>
+      <c r="C29" s="1">
+        <v>100</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" s="1">
+        <v>2</v>
+      </c>
+      <c r="N29" s="6"/>
+      <c r="S29" s="6"/>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A30" s="1">
+        <v>125</v>
+      </c>
+      <c r="B30" s="5">
+        <v>30010015</v>
+      </c>
+      <c r="C30" s="1">
+        <v>100</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2</v>
+      </c>
+      <c r="N30" s="6"/>
+      <c r="S30" s="6"/>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A31" s="1">
+        <v>126</v>
+      </c>
+      <c r="B31" s="1">
+        <v>20410111</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N31" s="6"/>
+      <c r="S31" s="6"/>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A32" s="1">
+        <v>127</v>
+      </c>
+      <c r="B32" s="1">
+        <v>20610111</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N32" s="6"/>
+      <c r="S32" s="6"/>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A33" s="1">
+        <v>128</v>
+      </c>
+      <c r="B33" s="1">
+        <v>20810111</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N33" s="6"/>
+      <c r="S33" s="6"/>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A34" s="1">
+        <v>129</v>
+      </c>
+      <c r="B34" s="1">
+        <v>20710111</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N34" s="6"/>
+      <c r="S34" s="6"/>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A35" s="1">
+        <v>130</v>
+      </c>
+      <c r="B35" s="1">
+        <v>20910111</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N35" s="6"/>
+      <c r="S35" s="6"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A36" s="1">
+        <v>131</v>
+      </c>
+      <c r="B36" s="1">
+        <v>20310111</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N36" s="6"/>
+      <c r="S36" s="6"/>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A37" s="1">
+        <v>132</v>
+      </c>
+      <c r="B37" s="1">
+        <v>60030032</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N37" s="6"/>
+      <c r="S37" s="6"/>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A38" s="1">
+        <v>133</v>
+      </c>
+      <c r="B38" s="1">
+        <v>60030022</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N38" s="6"/>
+      <c r="S38" s="6"/>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A39" s="1">
+        <v>134</v>
+      </c>
+      <c r="B39" s="1">
+        <v>60035068</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N39" s="6"/>
+      <c r="S39" s="6"/>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A40" s="1">
+        <v>135</v>
+      </c>
+      <c r="B40" s="1">
+        <v>60030004</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F40" s="6"/>
+      <c r="H40" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="N40" s="6"/>
+      <c r="S40" s="6"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A41" s="1">
+        <v>136</v>
+      </c>
+      <c r="B41" s="1">
+        <v>60030011</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1</v>
+      </c>
+      <c r="D41" s="1">
+        <v>3</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" s="6"/>
+      <c r="H41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N41" s="6"/>
+      <c r="S41" s="6"/>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A42" s="1">
+        <v>137</v>
+      </c>
+      <c r="B42" s="1">
+        <v>60030003</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="1">
+        <v>3</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F42" s="6"/>
+      <c r="H42" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="N42" s="6"/>
+      <c r="S42" s="6"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A43" s="1">
+        <v>138</v>
+      </c>
+      <c r="B43" s="1">
+        <v>60030006</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1</v>
+      </c>
+      <c r="D43" s="1">
+        <v>3</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F43" s="6"/>
+      <c r="H43" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N43" s="6"/>
+      <c r="S43" s="6"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A44" s="1">
+        <v>139</v>
+      </c>
+      <c r="B44" s="1">
+        <v>60030002</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F44" s="6"/>
+      <c r="H44" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A45" s="1">
+        <v>140</v>
+      </c>
+      <c r="B45" s="1">
+        <v>60030007</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1">
+        <v>3</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" s="6"/>
+      <c r="H45" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:19">
+      <c r="A46" s="1">
+        <v>141</v>
+      </c>
+      <c r="B46" s="1">
+        <v>60030005</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1</v>
+      </c>
+      <c r="D46" s="1">
+        <v>3</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A47" s="1">
+        <v>142</v>
+      </c>
+      <c r="B47" s="1">
+        <v>60030008</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F47" s="6"/>
+      <c r="H47" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A48" s="1">
+        <v>143</v>
+      </c>
+      <c r="B48" s="11">
+        <v>60030030</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1">
+        <v>4</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F48" s="6"/>
+      <c r="H48" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A49" s="1">
+        <v>144</v>
+      </c>
+      <c r="B49" s="11">
+        <v>60030031</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1</v>
+      </c>
+      <c r="D49" s="1">
+        <v>4</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F49" s="6"/>
+      <c r="H49" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A50" s="1">
+        <v>145</v>
+      </c>
+      <c r="B50" s="11">
+        <v>60030032</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1</v>
+      </c>
+      <c r="D50" s="1">
+        <v>4</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="F50" s="6"/>
+      <c r="H50" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A51" s="1">
+        <v>146</v>
+      </c>
+      <c r="B51" s="11">
+        <v>60030033</v>
+      </c>
+      <c r="C51" s="1">
+        <v>1</v>
+      </c>
+      <c r="D51" s="1">
+        <v>4</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F51" s="6"/>
+      <c r="H51" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A52" s="1">
+        <v>147</v>
+      </c>
+      <c r="B52" s="11">
+        <v>60030034</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1</v>
+      </c>
+      <c r="D52" s="1">
+        <v>4</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F52" s="6"/>
+      <c r="H52" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A53" s="1">
+        <v>148</v>
+      </c>
+      <c r="B53" s="1">
+        <v>3000104</v>
+      </c>
+      <c r="C53" s="1">
+        <v>1</v>
+      </c>
+      <c r="D53" s="1">
+        <v>5</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A54" s="1">
+        <v>149</v>
+      </c>
+      <c r="B54" s="5">
+        <v>30010001</v>
+      </c>
+      <c r="C54" s="1">
+        <v>20</v>
+      </c>
+      <c r="D54" s="1">
+        <v>5</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A55" s="1">
+        <v>150</v>
+      </c>
+      <c r="B55" s="5">
+        <v>30010002</v>
+      </c>
+      <c r="C55" s="1">
+        <v>20</v>
+      </c>
+      <c r="D55" s="1">
+        <v>5</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I55" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A56" s="1">
+        <v>151</v>
+      </c>
+      <c r="B56" s="5">
+        <v>30010006</v>
+      </c>
+      <c r="C56" s="1">
+        <v>20</v>
+      </c>
+      <c r="D56" s="1">
+        <v>5</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I56" s="1">
+        <v>1</v>
+      </c>
+      <c r="S56" s="6"/>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A57" s="1">
+        <v>152</v>
+      </c>
+      <c r="B57" s="5">
+        <v>30010012</v>
+      </c>
+      <c r="C57" s="1">
+        <v>20</v>
+      </c>
+      <c r="D57" s="1">
+        <v>5</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I57" s="1">
+        <v>2</v>
+      </c>
+      <c r="J57" s="7"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="7"/>
+      <c r="M57" s="7"/>
+      <c r="N57" s="6"/>
+      <c r="S57" s="6"/>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A58" s="1">
+        <v>153</v>
+      </c>
+      <c r="B58" s="5">
+        <v>30010015</v>
+      </c>
+      <c r="C58" s="1">
+        <v>20</v>
+      </c>
+      <c r="D58" s="1">
+        <v>5</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I58" s="1">
+        <v>2</v>
+      </c>
+      <c r="J58" s="7"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="7"/>
+      <c r="M58" s="7"/>
+      <c r="N58" s="6"/>
+      <c r="S58" s="6"/>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A59" s="1">
+        <v>154</v>
+      </c>
+      <c r="B59" s="5">
+        <v>30010003</v>
+      </c>
+      <c r="C59" s="1">
+        <v>20</v>
+      </c>
+      <c r="D59" s="1">
+        <v>5</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A60" s="1">
+        <v>155</v>
+      </c>
+      <c r="B60" s="5">
+        <v>30010007</v>
+      </c>
+      <c r="C60" s="1">
+        <v>20</v>
+      </c>
+      <c r="D60" s="1">
+        <v>5</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I60" s="1">
+        <v>1</v>
+      </c>
+      <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="N60" s="6"/>
+      <c r="S60" s="6"/>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A61" s="1">
+        <v>156</v>
+      </c>
+      <c r="B61" s="5">
+        <v>30010013</v>
+      </c>
+      <c r="C61" s="1">
+        <v>20</v>
+      </c>
+      <c r="D61" s="1">
+        <v>5</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I61" s="1">
+        <v>2</v>
+      </c>
+      <c r="J61" s="7"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="7"/>
+      <c r="M61" s="7"/>
+      <c r="N61" s="6"/>
+      <c r="S61" s="6"/>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A62" s="1">
+        <v>157</v>
+      </c>
+      <c r="B62" s="5">
+        <v>30010004</v>
+      </c>
+      <c r="C62" s="1">
+        <v>20</v>
+      </c>
+      <c r="D62" s="1">
+        <v>5</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A63" s="1">
+        <v>158</v>
+      </c>
+      <c r="B63" s="5">
+        <v>30010008</v>
+      </c>
+      <c r="C63" s="1">
+        <v>20</v>
+      </c>
+      <c r="D63" s="1">
+        <v>5</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I63" s="1">
+        <v>1</v>
+      </c>
+      <c r="L63" s="8"/>
+      <c r="M63" s="7"/>
+      <c r="N63" s="6"/>
+      <c r="S63" s="6"/>
+    </row>
+    <row r="64" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A64" s="1">
+        <v>159</v>
+      </c>
+      <c r="B64" s="5">
+        <v>30010014</v>
+      </c>
+      <c r="C64" s="1">
+        <v>20</v>
+      </c>
+      <c r="D64" s="1">
+        <v>5</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I64" s="1">
+        <v>2</v>
+      </c>
+      <c r="J64" s="7"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="7"/>
+      <c r="M64" s="7"/>
+      <c r="N64" s="6"/>
+      <c r="S64" s="6"/>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A65" s="1">
+        <v>160</v>
+      </c>
+      <c r="B65" s="5">
+        <v>30010005</v>
+      </c>
+      <c r="C65" s="1">
+        <v>20</v>
+      </c>
+      <c r="D65" s="1">
+        <v>5</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I65" s="1">
+        <v>1</v>
+      </c>
+      <c r="M65" s="8"/>
+      <c r="N65" s="6"/>
+      <c r="S65" s="6"/>
+    </row>
+    <row r="66" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A66" s="1">
+        <v>161</v>
+      </c>
+      <c r="B66" s="5">
+        <v>30010009</v>
+      </c>
+      <c r="C66" s="1">
+        <v>20</v>
+      </c>
+      <c r="D66" s="1">
+        <v>5</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I66" s="1">
+        <v>1</v>
+      </c>
+      <c r="K66" s="8"/>
+      <c r="L66" s="7"/>
+      <c r="M66" s="7"/>
+      <c r="N66" s="6"/>
+      <c r="S66" s="6"/>
+    </row>
+    <row r="67" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A67" s="1">
+        <v>162</v>
+      </c>
+      <c r="B67" s="5">
+        <v>30010001</v>
+      </c>
+      <c r="C67" s="1">
+        <v>100</v>
+      </c>
+      <c r="D67" s="1">
+        <v>5</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I67" s="1">
+        <v>1</v>
+      </c>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+      <c r="N67" s="6"/>
+      <c r="S67" s="6"/>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A68" s="1">
+        <v>163</v>
+      </c>
+      <c r="B68" s="5">
+        <v>30010002</v>
+      </c>
+      <c r="C68" s="1">
+        <v>100</v>
+      </c>
+      <c r="D68" s="1">
+        <v>5</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1</v>
+      </c>
+      <c r="K68" s="8"/>
+      <c r="L68" s="8"/>
+      <c r="N68" s="6"/>
+      <c r="S68" s="6"/>
+    </row>
+    <row r="69" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A69" s="1">
+        <v>164</v>
+      </c>
+      <c r="B69" s="5">
+        <v>30010003</v>
+      </c>
+      <c r="C69" s="1">
+        <v>100</v>
+      </c>
+      <c r="D69" s="1">
+        <v>5</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I69" s="1">
+        <v>1</v>
+      </c>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+      <c r="N69" s="6"/>
+      <c r="S69" s="6"/>
+    </row>
+    <row r="70" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A70" s="1">
+        <v>165</v>
+      </c>
+      <c r="B70" s="5">
+        <v>30010004</v>
+      </c>
+      <c r="C70" s="1">
+        <v>100</v>
+      </c>
+      <c r="D70" s="1">
+        <v>5</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I70" s="1">
+        <v>1</v>
+      </c>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="N70" s="6"/>
+      <c r="S70" s="6"/>
+    </row>
+    <row r="71" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A71" s="1">
+        <v>166</v>
+      </c>
+      <c r="B71" s="5">
+        <v>30010005</v>
+      </c>
+      <c r="C71" s="1">
+        <v>100</v>
+      </c>
+      <c r="D71" s="1">
+        <v>5</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I71" s="1">
+        <v>1</v>
+      </c>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+      <c r="N71" s="6"/>
+      <c r="S71" s="6"/>
+    </row>
+    <row r="72" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A72" s="1">
+        <v>167</v>
+      </c>
+      <c r="B72" s="5">
+        <v>30010006</v>
+      </c>
+      <c r="C72" s="1">
+        <v>100</v>
+      </c>
+      <c r="D72" s="1">
+        <v>5</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I72" s="1">
+        <v>1</v>
+      </c>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+      <c r="N72" s="6"/>
+      <c r="S72" s="6"/>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A73" s="1">
+        <v>168</v>
+      </c>
+      <c r="B73" s="5">
+        <v>30010007</v>
+      </c>
+      <c r="C73" s="1">
+        <v>100</v>
+      </c>
+      <c r="D73" s="1">
+        <v>5</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I73" s="1">
+        <v>1</v>
+      </c>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+      <c r="N73" s="6"/>
+      <c r="S73" s="6"/>
+    </row>
+    <row r="74" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A74" s="1">
+        <v>169</v>
+      </c>
+      <c r="B74" s="5">
+        <v>30010008</v>
+      </c>
+      <c r="C74" s="1">
+        <v>100</v>
+      </c>
+      <c r="D74" s="1">
+        <v>5</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I74" s="1">
+        <v>1</v>
+      </c>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="N74" s="6"/>
+      <c r="S74" s="6"/>
+    </row>
+    <row r="75" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A75" s="1">
+        <v>170</v>
+      </c>
+      <c r="B75" s="5">
+        <v>30010009</v>
+      </c>
+      <c r="C75" s="1">
+        <v>100</v>
+      </c>
+      <c r="D75" s="1">
+        <v>5</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I75" s="1">
+        <v>1</v>
+      </c>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+      <c r="N75" s="6"/>
+      <c r="S75" s="6"/>
+    </row>
+    <row r="76" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A76" s="1">
+        <v>171</v>
+      </c>
+      <c r="B76" s="5">
+        <v>30010012</v>
+      </c>
+      <c r="C76" s="1">
+        <v>100</v>
+      </c>
+      <c r="D76" s="1">
+        <v>5</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I76" s="1">
+        <v>2</v>
+      </c>
+      <c r="N76" s="6"/>
+      <c r="S76" s="6"/>
+    </row>
+    <row r="77" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A77" s="1">
+        <v>172</v>
+      </c>
+      <c r="B77" s="5">
+        <v>30010013</v>
+      </c>
+      <c r="C77" s="1">
+        <v>100</v>
+      </c>
+      <c r="D77" s="1">
+        <v>5</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I77" s="1">
+        <v>2</v>
+      </c>
+      <c r="N77" s="6"/>
+      <c r="S77" s="6"/>
+    </row>
+    <row r="78" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A78" s="1">
+        <v>173</v>
+      </c>
+      <c r="B78" s="5">
+        <v>30010014</v>
+      </c>
+      <c r="C78" s="1">
+        <v>100</v>
+      </c>
+      <c r="D78" s="1">
+        <v>5</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I78" s="1">
+        <v>2</v>
+      </c>
+      <c r="N78" s="6"/>
+      <c r="S78" s="6"/>
+    </row>
+    <row r="79" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A79" s="1">
+        <v>174</v>
+      </c>
+      <c r="B79" s="5">
+        <v>30010015</v>
+      </c>
+      <c r="C79" s="1">
+        <v>100</v>
+      </c>
+      <c r="D79" s="1">
+        <v>5</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I79" s="1">
+        <v>2</v>
+      </c>
+      <c r="N79" s="6"/>
+      <c r="S79" s="6"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="M43">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A$1:A$1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48:B49">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>2147483647</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50:B52">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+      <formula>2147483647</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M44:M52">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M18:M26 M15 M8:M9 M12">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11 M14 M16:M17 M27:M42">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M57:M58 M61 M64 M67:M75">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M60 M63 M65:M66 M76:M79">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_npcShop.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_npcShop.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="119">
   <si>
     <t>序号</t>
   </si>
@@ -749,6 +749,9 @@
   </si>
   <si>
     <t>冲击波卷轴</t>
+  </si>
+  <si>
+    <t>天雷闪之石</t>
   </si>
   <si>
     <t>101#50</t>
@@ -4157,7 +4160,7 @@
         <v>160</v>
       </c>
       <c r="B65" s="14">
-        <v>60030072</v>
+        <v>60030068</v>
       </c>
       <c r="C65" s="1">
         <v>1</v>
@@ -4166,7 +4169,7 @@
         <v>5</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>37</v>
@@ -5473,7 +5476,7 @@
         <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>40</v>
@@ -5502,7 +5505,7 @@
         <v>37</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>53</v>
@@ -5535,7 +5538,7 @@
         <v>37</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>42</v>
@@ -5570,7 +5573,7 @@
         <v>37</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>42</v>
@@ -5599,7 +5602,7 @@
         <v>37</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>55</v>
@@ -5632,7 +5635,7 @@
         <v>37</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>48</v>
@@ -5667,7 +5670,7 @@
         <v>37</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>44</v>
@@ -5699,7 +5702,7 @@
         <v>37</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>57</v>
@@ -5799,7 +5802,7 @@
         <v>32</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>42</v>
@@ -5832,7 +5835,7 @@
         <v>32</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>48</v>
@@ -5865,7 +5868,7 @@
         <v>32</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>62</v>
@@ -5898,7 +5901,7 @@
         <v>32</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>64</v>
@@ -5931,7 +5934,7 @@
         <v>32</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>66</v>
@@ -5964,7 +5967,7 @@
         <v>32</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>68</v>
@@ -5997,7 +6000,7 @@
         <v>32</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>70</v>
@@ -6061,7 +6064,7 @@
         <v>32</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>73</v>
@@ -6092,7 +6095,7 @@
         <v>32</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>75</v>
@@ -6148,10 +6151,10 @@
         <v>2</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>53</v>
@@ -6173,10 +6176,10 @@
         <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>53</v>
@@ -6198,10 +6201,10 @@
         <v>2</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>53</v>
@@ -6223,10 +6226,10 @@
         <v>2</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>53</v>
@@ -6248,10 +6251,10 @@
         <v>2</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>53</v>
@@ -6273,10 +6276,10 @@
         <v>2</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>53</v>
@@ -6298,7 +6301,7 @@
         <v>2</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>32</v>
@@ -6323,7 +6326,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>32</v>
@@ -6348,7 +6351,7 @@
         <v>2</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>32</v>
@@ -6373,11 +6376,11 @@
         <v>3</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F40" s="6"/>
       <c r="H40" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N40" s="6"/>
       <c r="S40" s="6"/>
@@ -6396,7 +6399,7 @@
         <v>3</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F41" s="6"/>
       <c r="H41" s="1" t="s">
@@ -6419,11 +6422,11 @@
         <v>3</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F42" s="6"/>
       <c r="H42" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N42" s="6"/>
       <c r="S42" s="6"/>
@@ -6442,7 +6445,7 @@
         <v>3</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F43" s="6"/>
       <c r="H43" s="1" t="s">
@@ -6465,11 +6468,11 @@
         <v>3</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F44" s="6"/>
       <c r="H44" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6486,11 +6489,11 @@
         <v>3</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F45" s="6"/>
       <c r="H45" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:19">
@@ -6507,10 +6510,10 @@
         <v>3</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6527,11 +6530,11 @@
         <v>3</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F47" s="6"/>
       <c r="H47" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6548,11 +6551,11 @@
         <v>4</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F48" s="6"/>
       <c r="H48" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6569,7 +6572,7 @@
         <v>4</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F49" s="6"/>
       <c r="H49" s="1" t="s">
@@ -6590,11 +6593,11 @@
         <v>4</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F50" s="6"/>
       <c r="H50" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6611,7 +6614,7 @@
         <v>4</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F51" s="6"/>
       <c r="H51" s="1" t="s">
@@ -6632,11 +6635,11 @@
         <v>4</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F52" s="6"/>
       <c r="H52" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6843,7 +6846,7 @@
         <v>37</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>40</v>
@@ -6872,7 +6875,7 @@
         <v>37</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>53</v>
@@ -6905,7 +6908,7 @@
         <v>37</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>42</v>
@@ -6940,7 +6943,7 @@
         <v>37</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>42</v>
@@ -6969,7 +6972,7 @@
         <v>37</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>55</v>
@@ -7002,7 +7005,7 @@
         <v>37</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>48</v>
@@ -7037,7 +7040,7 @@
         <v>37</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>44</v>
@@ -7069,7 +7072,7 @@
         <v>37</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>57</v>
@@ -7169,7 +7172,7 @@
         <v>32</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>42</v>
@@ -7202,7 +7205,7 @@
         <v>32</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>48</v>
@@ -7235,7 +7238,7 @@
         <v>32</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>62</v>
@@ -7268,7 +7271,7 @@
         <v>32</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>64</v>
@@ -7301,7 +7304,7 @@
         <v>32</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>66</v>
@@ -7334,7 +7337,7 @@
         <v>32</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>68</v>
@@ -7367,7 +7370,7 @@
         <v>32</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>70</v>
@@ -7431,7 +7434,7 @@
         <v>32</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>73</v>
@@ -7462,7 +7465,7 @@
         <v>32</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>75</v>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_npcShop.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_npcShop.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_npcShop" sheetId="1" r:id="rId1"/>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="134">
   <si>
     <t>序号</t>
   </si>
@@ -526,7 +531,7 @@
     <t>group</t>
   </si>
   <si>
-    <t>苹果</t>
+    <t>大量苹果</t>
   </si>
   <si>
     <t>checkLevel&gt;=9500&amp;&amp;checkLevel&lt;10001</t>
@@ -536,9 +541,6 @@
   </si>
   <si>
     <t>10010002#2#0#100</t>
-  </si>
-  <si>
-    <t>大量苹果</t>
   </si>
   <si>
     <t>小瓶治疗药水</t>
@@ -736,6 +738,60 @@
     <t>10010002#8.5#0#100</t>
   </si>
   <si>
+    <t>苹果</t>
+  </si>
+  <si>
+    <t>代币</t>
+  </si>
+  <si>
+    <t>绝版旗帜（非卖品）</t>
+  </si>
+  <si>
+    <t>玛雅之石</t>
+  </si>
+  <si>
+    <t>祝福宝石</t>
+  </si>
+  <si>
+    <t>灵魂宝石</t>
+  </si>
+  <si>
+    <t>生命宝石</t>
+  </si>
+  <si>
+    <t>创造宝石</t>
+  </si>
+  <si>
+    <t>黑龙波术</t>
+  </si>
+  <si>
+    <t>雷鸟术</t>
+  </si>
+  <si>
+    <t>星云火链卷轴</t>
+  </si>
+  <si>
+    <t>链雷咒羊皮纸</t>
+  </si>
+  <si>
+    <t>烈袭 羊皮纸</t>
+  </si>
+  <si>
+    <t>霹雳回旋斩之石</t>
+  </si>
+  <si>
+    <t>幻龙术</t>
+  </si>
+  <si>
+    <t>大天使积分</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>水幻兽 羊皮纸</t>
+  </si>
+  <si>
     <t>战斗箭筒</t>
   </si>
   <si>
@@ -745,9 +801,6 @@
     <t>多重箭之石</t>
   </si>
   <si>
-    <t>冲击技能书</t>
-  </si>
-  <si>
     <t>冲击波卷轴</t>
   </si>
   <si>
@@ -794,9 +847,6 @@
   </si>
   <si>
     <t>暗杀者之石</t>
-  </si>
-  <si>
-    <t>霹雳回旋斩之石</t>
   </si>
   <si>
     <t>钻云枪之石</t>
@@ -869,7 +919,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -909,6 +959,12 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1071,6 +1127,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1192,12 +1254,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1380,16 +1436,13 @@
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1398,37 +1451,37 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1443,74 +1496,77 @@
     <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1545,11 +1601,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1557,6 +1613,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2117,7 +2180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2253,7 +2316,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:19">
       <c r="A5" s="1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" s="5">
         <v>30010001</v>
@@ -2279,13 +2342,17 @@
       <c r="I5" s="1">
         <v>1</v>
       </c>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="N5" s="6"/>
+      <c r="S5" s="6"/>
     </row>
     <row r="6" ht="16.5" spans="1:19">
       <c r="A6" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B6" s="5">
-        <v>30010001</v>
+        <v>30010002</v>
       </c>
       <c r="C6" s="1">
         <v>20</v>
@@ -2297,28 +2364,24 @@
         <v>35</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="N6" s="6"/>
-      <c r="S6" s="6"/>
     </row>
     <row r="7" ht="16.5" spans="1:19">
       <c r="A7" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B7" s="5">
-        <v>30010002</v>
+        <v>30010003</v>
       </c>
       <c r="C7" s="1">
         <v>20</v>
@@ -2327,16 +2390,16 @@
         <v>1</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="G7" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
@@ -2344,10 +2407,10 @@
     </row>
     <row r="8" ht="16.5" spans="1:19">
       <c r="A8" s="1">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B8" s="5">
-        <v>30010003</v>
+        <v>30010004</v>
       </c>
       <c r="C8" s="1">
         <v>20</v>
@@ -2356,16 +2419,16 @@
         <v>1</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
@@ -2373,10 +2436,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:19">
       <c r="A9" s="1">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B9" s="5">
-        <v>30010004</v>
+        <v>30010005</v>
       </c>
       <c r="C9" s="1">
         <v>20</v>
@@ -2385,27 +2448,30 @@
         <v>1</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="6"/>
+      <c r="S9" s="6"/>
     </row>
     <row r="10" ht="16.5" spans="1:19">
       <c r="A10" s="1">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" s="5">
-        <v>30010005</v>
+        <v>30010012</v>
       </c>
       <c r="C10" s="1">
         <v>20</v>
@@ -2414,30 +2480,33 @@
         <v>1</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="I10" s="1">
-        <v>1</v>
-      </c>
-      <c r="M10" s="8"/>
+        <v>2</v>
+      </c>
+      <c r="J10" s="7"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
       <c r="N10" s="6"/>
       <c r="S10" s="6"/>
     </row>
     <row r="11" ht="16.5" spans="1:19">
       <c r="A11" s="1">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B11" s="5">
-        <v>30010012</v>
+        <v>30010013</v>
       </c>
       <c r="C11" s="1">
         <v>20</v>
@@ -2449,13 +2518,13 @@
         <v>45</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I11" s="1">
         <v>2</v>
@@ -2469,10 +2538,10 @@
     </row>
     <row r="12" ht="16.5" spans="1:19">
       <c r="A12" s="1">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B12" s="5">
-        <v>30010013</v>
+        <v>30010014</v>
       </c>
       <c r="C12" s="1">
         <v>20</v>
@@ -2484,13 +2553,13 @@
         <v>46</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I12" s="1">
         <v>2</v>
@@ -2504,10 +2573,10 @@
     </row>
     <row r="13" ht="16.5" spans="1:19">
       <c r="A13" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B13" s="5">
-        <v>30010014</v>
+        <v>30010015</v>
       </c>
       <c r="C13" s="1">
         <v>20</v>
@@ -2516,16 +2585,16 @@
         <v>1</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I13" s="1">
         <v>2</v>
@@ -2539,10 +2608,10 @@
     </row>
     <row r="14" ht="16.5" spans="1:19">
       <c r="A14" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="5">
-        <v>30010015</v>
+        <v>30010006</v>
       </c>
       <c r="C14" s="1">
         <v>20</v>
@@ -2551,33 +2620,28 @@
         <v>1</v>
       </c>
       <c r="E14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="I14" s="1">
-        <v>2</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="6"/>
+        <v>1</v>
+      </c>
       <c r="S14" s="6"/>
     </row>
     <row r="15" ht="16.5" spans="1:19">
       <c r="A15" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B15" s="5">
-        <v>30010006</v>
+        <v>30010007</v>
       </c>
       <c r="C15" s="1">
         <v>20</v>
@@ -2589,25 +2653,28 @@
         <v>51</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="6"/>
       <c r="S15" s="6"/>
     </row>
     <row r="16" ht="16.5" spans="1:19">
       <c r="A16" s="1">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B16" s="5">
-        <v>30010007</v>
+        <v>30010008</v>
       </c>
       <c r="C16" s="1">
         <v>20</v>
@@ -2616,31 +2683,31 @@
         <v>1</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
+      <c r="M16" s="7"/>
       <c r="N16" s="6"/>
       <c r="S16" s="6"/>
     </row>
     <row r="17" ht="16.5" spans="1:19">
       <c r="A17" s="1">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B17" s="5">
-        <v>30010008</v>
+        <v>30010009</v>
       </c>
       <c r="C17" s="1">
         <v>20</v>
@@ -2649,31 +2716,32 @@
         <v>1</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I17" s="1">
         <v>1</v>
       </c>
-      <c r="L17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="7"/>
       <c r="M17" s="7"/>
       <c r="N17" s="6"/>
       <c r="S17" s="6"/>
     </row>
     <row r="18" ht="16.5" spans="1:19">
       <c r="A18" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B18" s="5">
-        <v>30010009</v>
+        <v>30010002</v>
       </c>
       <c r="C18" s="1">
         <v>20</v>
@@ -2682,32 +2750,31 @@
         <v>1</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="I18" s="1">
         <v>1</v>
       </c>
       <c r="K18" s="8"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
+      <c r="L18" s="8"/>
       <c r="N18" s="6"/>
       <c r="S18" s="6"/>
     </row>
     <row r="19" ht="16.5" spans="1:19">
       <c r="A19" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B19" s="5">
-        <v>30010002</v>
+        <v>30010003</v>
       </c>
       <c r="C19" s="1">
         <v>20</v>
@@ -2725,7 +2792,7 @@
         <v>33</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
@@ -2737,10 +2804,10 @@
     </row>
     <row r="20" ht="16.5" spans="1:19">
       <c r="A20" s="1">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B20" s="5">
-        <v>30010003</v>
+        <v>30010004</v>
       </c>
       <c r="C20" s="1">
         <v>20</v>
@@ -2758,7 +2825,7 @@
         <v>33</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
@@ -2770,10 +2837,10 @@
     </row>
     <row r="21" ht="16.5" spans="1:19">
       <c r="A21" s="1">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B21" s="5">
-        <v>30010004</v>
+        <v>30010005</v>
       </c>
       <c r="C21" s="1">
         <v>20</v>
@@ -2791,7 +2858,7 @@
         <v>33</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
@@ -2803,10 +2870,10 @@
     </row>
     <row r="22" ht="16.5" spans="1:19">
       <c r="A22" s="1">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B22" s="5">
-        <v>30010005</v>
+        <v>30010006</v>
       </c>
       <c r="C22" s="1">
         <v>20</v>
@@ -2815,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>32</v>
@@ -2824,7 +2891,7 @@
         <v>33</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
@@ -2836,10 +2903,10 @@
     </row>
     <row r="23" ht="16.5" spans="1:19">
       <c r="A23" s="1">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B23" s="5">
-        <v>30010006</v>
+        <v>30010007</v>
       </c>
       <c r="C23" s="1">
         <v>20</v>
@@ -2848,7 +2915,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>32</v>
@@ -2857,7 +2924,7 @@
         <v>33</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I23" s="1">
         <v>1</v>
@@ -2869,10 +2936,10 @@
     </row>
     <row r="24" ht="16.5" spans="1:19">
       <c r="A24" s="1">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B24" s="5">
-        <v>30010007</v>
+        <v>30010008</v>
       </c>
       <c r="C24" s="1">
         <v>20</v>
@@ -2881,7 +2948,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>32</v>
@@ -2890,7 +2957,7 @@
         <v>33</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
@@ -2902,10 +2969,10 @@
     </row>
     <row r="25" ht="16.5" spans="1:19">
       <c r="A25" s="1">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B25" s="5">
-        <v>30010008</v>
+        <v>30010009</v>
       </c>
       <c r="C25" s="1">
         <v>20</v>
@@ -2914,7 +2981,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>32</v>
@@ -2923,7 +2990,7 @@
         <v>33</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
@@ -2935,10 +3002,10 @@
     </row>
     <row r="26" ht="16.5" spans="1:19">
       <c r="A26" s="1">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B26" s="5">
-        <v>30010009</v>
+        <v>30010012</v>
       </c>
       <c r="C26" s="1">
         <v>20</v>
@@ -2947,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>32</v>
@@ -2956,22 +3023,20 @@
         <v>33</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="I26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
+        <v>2</v>
+      </c>
       <c r="N26" s="6"/>
       <c r="S26" s="6"/>
     </row>
     <row r="27" ht="16.5" spans="1:19">
       <c r="A27" s="1">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B27" s="5">
-        <v>30010012</v>
+        <v>30010013</v>
       </c>
       <c r="C27" s="1">
         <v>20</v>
@@ -2989,7 +3054,7 @@
         <v>33</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="I27" s="1">
         <v>2</v>
@@ -2999,10 +3064,10 @@
     </row>
     <row r="28" ht="16.5" spans="1:19">
       <c r="A28" s="1">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B28" s="5">
-        <v>30010013</v>
+        <v>30010014</v>
       </c>
       <c r="C28" s="1">
         <v>20</v>
@@ -3011,7 +3076,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>32</v>
@@ -3020,7 +3085,7 @@
         <v>33</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I28" s="1">
         <v>2</v>
@@ -3030,10 +3095,10 @@
     </row>
     <row r="29" ht="16.5" spans="1:19">
       <c r="A29" s="1">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B29" s="5">
-        <v>30010014</v>
+        <v>30010015</v>
       </c>
       <c r="C29" s="1">
         <v>20</v>
@@ -3042,7 +3107,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>32</v>
@@ -3051,7 +3116,7 @@
         <v>33</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I29" s="1">
         <v>2</v>
@@ -3061,19 +3126,19 @@
     </row>
     <row r="30" ht="16.5" spans="1:19">
       <c r="A30" s="1">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>30010015</v>
+        <v>30010001</v>
       </c>
       <c r="C30" s="1">
         <v>20</v>
       </c>
       <c r="D30" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>32</v>
@@ -3082,29 +3147,27 @@
         <v>33</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="I30" s="1">
-        <v>2</v>
-      </c>
-      <c r="N30" s="6"/>
-      <c r="S30" s="6"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="31" ht="16.5" spans="1:19">
       <c r="A31" s="1">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B31" s="5">
-        <v>30010015</v>
+        <v>30010001</v>
       </c>
       <c r="C31" s="1">
         <v>20</v>
       </c>
       <c r="D31" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>32</v>
@@ -3113,102 +3176,109 @@
         <v>33</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I31" s="1">
-        <v>2</v>
-      </c>
-      <c r="J31" s="7"/>
+        <v>1</v>
+      </c>
       <c r="K31" s="8"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
+      <c r="L31" s="8"/>
       <c r="N31" s="6"/>
       <c r="S31" s="6"/>
     </row>
     <row r="32" ht="16.5" spans="1:19">
       <c r="A32" s="1">
-        <v>127</v>
-      </c>
-      <c r="B32" s="1">
-        <v>3000104</v>
+        <v>128</v>
+      </c>
+      <c r="B32" s="5">
+        <v>30010002</v>
       </c>
       <c r="C32" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>78</v>
+        <v>5</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="F32" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>79</v>
+      <c r="I32" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:19">
       <c r="A33" s="1">
-        <v>128</v>
-      </c>
-      <c r="B33" s="14">
-        <v>60030067</v>
+        <v>129</v>
+      </c>
+      <c r="B33" s="5">
+        <v>30010003</v>
       </c>
       <c r="C33" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>80</v>
+        <v>5</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>79</v>
+        <v>39</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:19">
       <c r="A34" s="1">
-        <v>129</v>
-      </c>
-      <c r="B34" s="14">
-        <v>60030072</v>
+        <v>130</v>
+      </c>
+      <c r="B34" s="5">
+        <v>30010004</v>
       </c>
       <c r="C34" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>81</v>
+        <v>5</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>79</v>
+        <v>41</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:19">
       <c r="A35" s="1">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="5">
-        <v>30010001</v>
+        <v>30010005</v>
       </c>
       <c r="C35" s="1">
         <v>20</v>
@@ -3217,27 +3287,30 @@
         <v>5</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I35" s="1">
         <v>1</v>
       </c>
+      <c r="M35" s="8"/>
+      <c r="N35" s="6"/>
+      <c r="S35" s="6"/>
     </row>
     <row r="36" ht="16.5" spans="1:19">
       <c r="A36" s="1">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
-        <v>30010001</v>
+        <v>30010012</v>
       </c>
       <c r="C36" s="1">
         <v>20</v>
@@ -3246,31 +3319,33 @@
         <v>5</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I36" s="1">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J36" s="7"/>
       <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
       <c r="N36" s="6"/>
       <c r="S36" s="6"/>
     </row>
     <row r="37" ht="16.5" spans="1:19">
       <c r="A37" s="1">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" s="5">
-        <v>30010002</v>
+        <v>30010013</v>
       </c>
       <c r="C37" s="1">
         <v>20</v>
@@ -3279,27 +3354,33 @@
         <v>5</v>
       </c>
       <c r="E37" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="G37" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I37" s="1">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J37" s="7"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="6"/>
+      <c r="S37" s="6"/>
     </row>
     <row r="38" ht="16.5" spans="1:19">
       <c r="A38" s="1">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B38" s="5">
-        <v>30010003</v>
+        <v>30010014</v>
       </c>
       <c r="C38" s="1">
         <v>20</v>
@@ -3308,27 +3389,33 @@
         <v>5</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I38" s="1">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J38" s="7"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="6"/>
+      <c r="S38" s="6"/>
     </row>
     <row r="39" ht="16.5" spans="1:19">
       <c r="A39" s="1">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B39" s="5">
-        <v>30010004</v>
+        <v>30010015</v>
       </c>
       <c r="C39" s="1">
         <v>20</v>
@@ -3337,27 +3424,33 @@
         <v>5</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I39" s="1">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J39" s="7"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="6"/>
+      <c r="S39" s="6"/>
     </row>
     <row r="40" ht="16.5" spans="1:19">
       <c r="A40" s="1">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B40" s="5">
-        <v>30010005</v>
+        <v>30010006</v>
       </c>
       <c r="C40" s="1">
         <v>20</v>
@@ -3366,30 +3459,28 @@
         <v>5</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
       </c>
-      <c r="M40" s="8"/>
-      <c r="N40" s="6"/>
       <c r="S40" s="6"/>
     </row>
     <row r="41" ht="16.5" spans="1:19">
       <c r="A41" s="1">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B41" s="5">
-        <v>30010012</v>
+        <v>30010007</v>
       </c>
       <c r="C41" s="1">
         <v>20</v>
@@ -3398,33 +3489,31 @@
         <v>5</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I41" s="1">
-        <v>2</v>
-      </c>
-      <c r="J41" s="7"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
       <c r="N41" s="6"/>
       <c r="S41" s="6"/>
     </row>
     <row r="42" ht="16.5" spans="1:19">
       <c r="A42" s="1">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B42" s="5">
-        <v>30010013</v>
+        <v>30010008</v>
       </c>
       <c r="C42" s="1">
         <v>20</v>
@@ -3433,33 +3522,31 @@
         <v>5</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I42" s="1">
-        <v>2</v>
-      </c>
-      <c r="J42" s="7"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="L42" s="8"/>
       <c r="M42" s="7"/>
       <c r="N42" s="6"/>
       <c r="S42" s="6"/>
     </row>
     <row r="43" ht="16.5" spans="1:19">
       <c r="A43" s="1">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B43" s="5">
-        <v>30010014</v>
+        <v>30010009</v>
       </c>
       <c r="C43" s="1">
         <v>20</v>
@@ -3468,21 +3555,20 @@
         <v>5</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I43" s="1">
-        <v>2</v>
-      </c>
-      <c r="J43" s="7"/>
+        <v>1</v>
+      </c>
       <c r="K43" s="8"/>
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
@@ -3491,10 +3577,10 @@
     </row>
     <row r="44" ht="16.5" spans="1:19">
       <c r="A44" s="1">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B44" s="5">
-        <v>30010015</v>
+        <v>30010002</v>
       </c>
       <c r="C44" s="1">
         <v>20</v>
@@ -3503,33 +3589,31 @@
         <v>5</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F44" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="I44" s="1">
-        <v>2</v>
-      </c>
-      <c r="J44" s="7"/>
+        <v>1</v>
+      </c>
       <c r="K44" s="8"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
+      <c r="L44" s="8"/>
       <c r="N44" s="6"/>
       <c r="S44" s="6"/>
     </row>
     <row r="45" ht="16.5" spans="1:19">
       <c r="A45" s="1">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B45" s="5">
-        <v>30010006</v>
+        <v>30010003</v>
       </c>
       <c r="C45" s="1">
         <v>20</v>
@@ -3538,28 +3622,31 @@
         <v>5</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="I45" s="1">
         <v>1</v>
       </c>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="N45" s="6"/>
       <c r="S45" s="6"/>
     </row>
     <row r="46" ht="16.5" spans="1:19">
       <c r="A46" s="1">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B46" s="5">
-        <v>30010007</v>
+        <v>30010004</v>
       </c>
       <c r="C46" s="1">
         <v>20</v>
@@ -3568,31 +3655,31 @@
         <v>5</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="I46" s="1">
         <v>1</v>
       </c>
+      <c r="K46" s="8"/>
       <c r="L46" s="8"/>
-      <c r="M46" s="8"/>
       <c r="N46" s="6"/>
       <c r="S46" s="6"/>
     </row>
     <row r="47" ht="16.5" spans="1:19">
       <c r="A47" s="1">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B47" s="5">
-        <v>30010008</v>
+        <v>30010005</v>
       </c>
       <c r="C47" s="1">
         <v>20</v>
@@ -3601,31 +3688,31 @@
         <v>5</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I47" s="1">
         <v>1</v>
       </c>
+      <c r="K47" s="8"/>
       <c r="L47" s="8"/>
-      <c r="M47" s="7"/>
       <c r="N47" s="6"/>
       <c r="S47" s="6"/>
     </row>
     <row r="48" ht="16.5" spans="1:19">
       <c r="A48" s="1">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B48" s="5">
-        <v>30010009</v>
+        <v>30010006</v>
       </c>
       <c r="C48" s="1">
         <v>20</v>
@@ -3634,32 +3721,31 @@
         <v>5</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I48" s="1">
         <v>1</v>
       </c>
       <c r="K48" s="8"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
+      <c r="L48" s="8"/>
       <c r="N48" s="6"/>
       <c r="S48" s="6"/>
     </row>
     <row r="49" ht="16.5" spans="1:19">
       <c r="A49" s="1">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B49" s="5">
-        <v>30010002</v>
+        <v>30010007</v>
       </c>
       <c r="C49" s="1">
         <v>20</v>
@@ -3668,7 +3754,7 @@
         <v>5</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>32</v>
@@ -3677,7 +3763,7 @@
         <v>33</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="I49" s="1">
         <v>1</v>
@@ -3689,10 +3775,10 @@
     </row>
     <row r="50" ht="16.5" spans="1:19">
       <c r="A50" s="1">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B50" s="5">
-        <v>30010003</v>
+        <v>30010008</v>
       </c>
       <c r="C50" s="1">
         <v>20</v>
@@ -3701,7 +3787,7 @@
         <v>5</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>32</v>
@@ -3710,7 +3796,7 @@
         <v>33</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="I50" s="1">
         <v>1</v>
@@ -3722,10 +3808,10 @@
     </row>
     <row r="51" ht="16.5" spans="1:19">
       <c r="A51" s="1">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B51" s="5">
-        <v>30010004</v>
+        <v>30010009</v>
       </c>
       <c r="C51" s="1">
         <v>20</v>
@@ -3734,7 +3820,7 @@
         <v>5</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>32</v>
@@ -3743,7 +3829,7 @@
         <v>33</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="I51" s="1">
         <v>1</v>
@@ -3755,10 +3841,10 @@
     </row>
     <row r="52" ht="16.5" spans="1:19">
       <c r="A52" s="1">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B52" s="5">
-        <v>30010005</v>
+        <v>30010012</v>
       </c>
       <c r="C52" s="1">
         <v>20</v>
@@ -3767,7 +3853,7 @@
         <v>5</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>32</v>
@@ -3776,22 +3862,20 @@
         <v>33</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="I52" s="1">
-        <v>1</v>
-      </c>
-      <c r="K52" s="8"/>
-      <c r="L52" s="8"/>
+        <v>2</v>
+      </c>
       <c r="N52" s="6"/>
       <c r="S52" s="6"/>
     </row>
     <row r="53" ht="16.5" spans="1:19">
       <c r="A53" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B53" s="5">
-        <v>30010006</v>
+        <v>30010013</v>
       </c>
       <c r="C53" s="1">
         <v>20</v>
@@ -3800,7 +3884,7 @@
         <v>5</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>32</v>
@@ -3809,22 +3893,20 @@
         <v>33</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I53" s="1">
-        <v>1</v>
-      </c>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
+        <v>2</v>
+      </c>
       <c r="N53" s="6"/>
       <c r="S53" s="6"/>
     </row>
     <row r="54" ht="16.5" spans="1:19">
       <c r="A54" s="1">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B54" s="5">
-        <v>30010007</v>
+        <v>30010014</v>
       </c>
       <c r="C54" s="1">
         <v>20</v>
@@ -3833,7 +3915,7 @@
         <v>5</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>32</v>
@@ -3842,22 +3924,20 @@
         <v>33</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="I54" s="1">
-        <v>1</v>
-      </c>
-      <c r="K54" s="8"/>
-      <c r="L54" s="8"/>
+        <v>2</v>
+      </c>
       <c r="N54" s="6"/>
       <c r="S54" s="6"/>
     </row>
     <row r="55" ht="16.5" spans="1:19">
       <c r="A55" s="1">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B55" s="5">
-        <v>30010008</v>
+        <v>30010015</v>
       </c>
       <c r="C55" s="1">
         <v>20</v>
@@ -3866,7 +3946,7 @@
         <v>5</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>32</v>
@@ -3875,67 +3955,61 @@
         <v>33</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I55" s="1">
-        <v>1</v>
-      </c>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
+        <v>2</v>
+      </c>
       <c r="N55" s="6"/>
       <c r="S55" s="6"/>
     </row>
-    <row r="56" ht="16.5" spans="1:19">
+    <row r="56" customFormat="1" ht="16.5" spans="1:19">
       <c r="A56" s="1">
-        <v>151</v>
-      </c>
-      <c r="B56" s="5">
-        <v>30010009</v>
+        <v>152</v>
+      </c>
+      <c r="B56" s="15">
+        <v>30510308</v>
       </c>
       <c r="C56" s="1">
-        <v>20</v>
+        <v>10000</v>
       </c>
       <c r="D56" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I56" s="1">
-        <v>1</v>
-      </c>
-      <c r="K56" s="8"/>
-      <c r="L56" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="I56" s="1"/>
       <c r="N56" s="6"/>
       <c r="S56" s="6"/>
     </row>
-    <row r="57" ht="16.5" spans="1:19">
+    <row r="57" customFormat="1" ht="16.5" spans="1:19">
       <c r="A57" s="1">
-        <v>152</v>
-      </c>
-      <c r="B57" s="5">
-        <v>30010012</v>
+        <v>153</v>
+      </c>
+      <c r="B57" s="16">
+        <v>23000099</v>
       </c>
       <c r="C57" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D57" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>33</v>
@@ -3943,306 +4017,661 @@
       <c r="H57" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I57" s="1">
-        <v>2</v>
-      </c>
+      <c r="I57" s="1"/>
       <c r="N57" s="6"/>
       <c r="S57" s="6"/>
     </row>
-    <row r="58" ht="16.5" spans="1:19">
+    <row r="58" customFormat="1" ht="16.5" spans="1:19">
       <c r="A58" s="1">
-        <v>153</v>
-      </c>
-      <c r="B58" s="5">
-        <v>30010013</v>
+        <v>154</v>
+      </c>
+      <c r="B58" s="14">
+        <v>1253000199</v>
       </c>
       <c r="C58" s="1">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="D58" s="1">
-        <v>5</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I58" s="1">
-        <v>2</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I58" s="1"/>
       <c r="N58" s="6"/>
       <c r="S58" s="6"/>
     </row>
-    <row r="59" ht="16.5" spans="1:19">
+    <row r="59" customFormat="1" ht="16.5" spans="1:19">
       <c r="A59" s="1">
-        <v>154</v>
-      </c>
-      <c r="B59" s="5">
-        <v>30010014</v>
+        <v>155</v>
+      </c>
+      <c r="B59" s="14">
+        <v>1253000299</v>
       </c>
       <c r="C59" s="1">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="D59" s="1">
-        <v>5</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>74</v>
+        <v>1</v>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I59" s="1">
-        <v>2</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I59" s="1"/>
       <c r="N59" s="6"/>
       <c r="S59" s="6"/>
     </row>
-    <row r="60" ht="16.5" spans="1:19">
+    <row r="60" customFormat="1" ht="16.5" spans="1:19">
       <c r="A60" s="1">
-        <v>155</v>
-      </c>
-      <c r="B60" s="5">
-        <v>30010015</v>
+        <v>156</v>
+      </c>
+      <c r="B60" s="14">
+        <v>1253000399</v>
       </c>
       <c r="C60" s="1">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="D60" s="1">
-        <v>5</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>76</v>
+        <v>1</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I60" s="1">
-        <v>2</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I60" s="1"/>
       <c r="N60" s="6"/>
       <c r="S60" s="6"/>
     </row>
-    <row r="61" ht="16.5" spans="1:19">
+    <row r="61" customFormat="1" ht="16.5" spans="1:19">
       <c r="A61" s="1">
-        <v>156</v>
-      </c>
-      <c r="B61" s="5">
-        <v>30010015</v>
+        <v>157</v>
+      </c>
+      <c r="B61" s="14">
+        <v>1253000499</v>
       </c>
       <c r="C61" s="1">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="D61" s="1">
-        <v>5</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I61" s="1">
-        <v>2</v>
-      </c>
-      <c r="J61" s="7"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="7"/>
-      <c r="M61" s="7"/>
+        <v>34</v>
+      </c>
+      <c r="I61" s="1"/>
       <c r="N61" s="6"/>
       <c r="S61" s="6"/>
     </row>
-    <row r="62" ht="16.5" spans="1:19">
+    <row r="62" customFormat="1" ht="16.5" spans="1:19">
       <c r="A62" s="1">
-        <v>157</v>
-      </c>
-      <c r="B62" s="1">
-        <v>3000104</v>
+        <v>158</v>
+      </c>
+      <c r="B62" s="14">
+        <v>1253000599</v>
       </c>
       <c r="C62" s="1">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="D62" s="1">
-        <v>5</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>78</v>
+        <v>1</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>84</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:19">
+        <v>34</v>
+      </c>
+      <c r="I62" s="1"/>
+      <c r="N62" s="6"/>
+      <c r="S62" s="6"/>
+    </row>
+    <row r="63" customFormat="1" ht="16.5" spans="1:19">
       <c r="A63" s="1">
-        <v>158</v>
-      </c>
-      <c r="B63" s="14">
-        <v>60030067</v>
+        <v>159</v>
+      </c>
+      <c r="B63" s="17">
+        <v>60030009</v>
       </c>
       <c r="C63" s="1">
         <v>1</v>
       </c>
       <c r="D63" s="1">
-        <v>5</v>
-      </c>
-      <c r="E63" s="15" t="s">
-        <v>80</v>
+        <v>1</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="64" ht="16.5" spans="1:19">
+        <v>34</v>
+      </c>
+      <c r="I63" s="1"/>
+      <c r="N63" s="6"/>
+      <c r="S63" s="6"/>
+    </row>
+    <row r="64" customFormat="1" ht="16.5" spans="1:19">
       <c r="A64" s="1">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B64" s="14">
-        <v>60030072</v>
+        <v>61007003</v>
       </c>
       <c r="C64" s="1">
         <v>1</v>
       </c>
       <c r="D64" s="1">
-        <v>5</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>86</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65" s="13" customFormat="1" ht="16.5" spans="1:8">
+        <v>34</v>
+      </c>
+      <c r="I64" s="1"/>
+      <c r="N64" s="6"/>
+      <c r="S64" s="6"/>
+    </row>
+    <row r="65" customFormat="1" ht="16.5" spans="1:19">
       <c r="A65" s="1">
-        <v>160</v>
-      </c>
-      <c r="B65" s="14">
-        <v>60030068</v>
+        <v>161</v>
+      </c>
+      <c r="B65" s="15">
+        <v>60035100</v>
       </c>
       <c r="C65" s="1">
         <v>1</v>
       </c>
       <c r="D65" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>79</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I65" s="1"/>
+      <c r="N65" s="6"/>
+      <c r="S65" s="6"/>
+    </row>
+    <row r="66" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A66" s="1">
+        <v>162</v>
+      </c>
+      <c r="B66" s="15">
+        <v>60035100</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I66" s="1"/>
+      <c r="N66" s="6"/>
+      <c r="S66" s="6"/>
+    </row>
+    <row r="67" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A67" s="1">
+        <v>163</v>
+      </c>
+      <c r="B67" s="15">
+        <v>60035083</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I67" s="1"/>
+      <c r="N67" s="6"/>
+      <c r="S67" s="6"/>
+    </row>
+    <row r="68" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A68" s="1">
+        <v>164</v>
+      </c>
+      <c r="B68" s="17">
+        <v>60030022</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I68" s="1"/>
+      <c r="N68" s="6"/>
+      <c r="S68" s="6"/>
+    </row>
+    <row r="69" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A69" s="1">
+        <v>165</v>
+      </c>
+      <c r="B69" s="14">
+        <v>61007001</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I69" s="1"/>
+      <c r="N69" s="6"/>
+      <c r="S69" s="6"/>
+    </row>
+    <row r="70" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A70" s="1">
+        <v>166</v>
+      </c>
+      <c r="B70" s="15">
+        <v>10210001</v>
+      </c>
+      <c r="C70" s="1">
+        <v>999</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I70" s="1"/>
+      <c r="N70" s="6"/>
+      <c r="S70" s="6"/>
+    </row>
+    <row r="71" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A71" s="1">
+        <v>167</v>
+      </c>
+      <c r="B71" s="15">
+        <v>100000007</v>
+      </c>
+      <c r="C71" s="1">
+        <v>1</v>
+      </c>
+      <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="N71" s="6"/>
+      <c r="S71" s="6"/>
+    </row>
+    <row r="72" ht="16.5" spans="1:19">
+      <c r="A72" s="1">
+        <v>168</v>
+      </c>
+      <c r="B72" s="14">
+        <v>1263508699</v>
+      </c>
+      <c r="C72" s="1">
+        <v>1</v>
+      </c>
+      <c r="D72" s="1">
+        <v>1</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="73" ht="16.5" spans="1:19">
+      <c r="A73" s="1">
+        <v>169</v>
+      </c>
+      <c r="B73" s="14">
+        <v>1263509299</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1</v>
+      </c>
+      <c r="D73" s="1">
+        <v>1</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:19">
+      <c r="C74" s="18"/>
+      <c r="D74" s="14"/>
+    </row>
+    <row r="75" ht="16.5" spans="1:19">
+      <c r="C75" s="15"/>
+      <c r="D75" s="15"/>
+    </row>
+    <row r="76" ht="16.5" spans="1:19">
+      <c r="B76" s="14"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="15"/>
+    </row>
+    <row r="77" ht="16.5" spans="1:19">
+      <c r="B77" s="14"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="15"/>
+    </row>
+    <row r="78" ht="16.5" spans="1:19">
+      <c r="B78" s="14"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="17"/>
+    </row>
+    <row r="79" ht="16.5" spans="1:19">
+      <c r="B79" s="14"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="14"/>
+    </row>
+    <row r="80" ht="16.5" spans="1:19">
+      <c r="B80" s="14"/>
+      <c r="C80" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M31">
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M56">
+    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="109"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M57">
+    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M58">
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="100"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M59">
+    <cfRule type="duplicateValues" dxfId="0" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="97"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M60">
+    <cfRule type="duplicateValues" dxfId="0" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M61">
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M62">
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M63">
+    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64">
     <cfRule type="duplicateValues" dxfId="0" priority="46"/>
     <cfRule type="duplicateValues" dxfId="1" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B33">
+  <conditionalFormatting sqref="M64">
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B65">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M65">
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B66">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M66">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
     <cfRule type="duplicateValues" dxfId="1" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M34">
-    <cfRule type="duplicateValues" dxfId="1" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M61">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
+  <conditionalFormatting sqref="B67">
     <cfRule type="duplicateValues" dxfId="0" priority="36"/>
     <cfRule type="duplicateValues" dxfId="1" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="27"/>
+  <conditionalFormatting sqref="M67">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M64">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
+  <conditionalFormatting sqref="M68">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A65">
+  <conditionalFormatting sqref="B69">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M69">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B70">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M70">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
     <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B65">
+  <conditionalFormatting sqref="M71">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B72">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M65">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  <conditionalFormatting sqref="D74">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A64 A66:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
+  <conditionalFormatting sqref="C75">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6 M11:M14 M19:M26">
+  <conditionalFormatting sqref="D75">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D76">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D77">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D79">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A70:A73">
+    <cfRule type="duplicateValues" dxfId="1" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58:B62">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B76:B80">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A69 A74:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="203"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5 M10:M13 M18:M25">
+    <cfRule type="duplicateValues" dxfId="1" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="261"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M9 M15:M17 M26:M29">
+    <cfRule type="duplicateValues" dxfId="1" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="263"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M31 M36:M39 M44:M51">
     <cfRule type="duplicateValues" dxfId="1" priority="149"/>
     <cfRule type="duplicateValues" dxfId="0" priority="150"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M10 M16:M18 M27:M30 M33">
+  <conditionalFormatting sqref="M35 M41:M43 M52:M55">
     <cfRule type="duplicateValues" dxfId="1" priority="151"/>
     <cfRule type="duplicateValues" dxfId="0" priority="152"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M36 M41:M44 M49:M56">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M40 M46:M48 M57:M60 M63">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4252,14 +4681,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B111"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="1"/>
+  <dimension ref="A1:H115"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.7142857142857"/>
+    <col min="2" max="2" width="29.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="12">
+      <c r="A1" s="13">
         <v>30010001</v>
       </c>
       <c r="B1">
@@ -4267,7 +4697,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="12">
+      <c r="A2" s="13">
         <v>30010002</v>
       </c>
       <c r="B2">
@@ -4275,7 +4705,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="12">
+      <c r="A3" s="13">
         <v>30010003</v>
       </c>
       <c r="B3">
@@ -4283,7 +4713,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>30010004</v>
       </c>
       <c r="B4">
@@ -4291,7 +4721,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="12">
+      <c r="A5" s="13">
         <v>30010005</v>
       </c>
       <c r="B5">
@@ -4299,7 +4729,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="12">
+      <c r="A6" s="13">
         <v>30010006</v>
       </c>
       <c r="B6">
@@ -4307,7 +4737,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="12">
+      <c r="A7" s="13">
         <v>30010007</v>
       </c>
       <c r="B7">
@@ -4315,7 +4745,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="12">
+      <c r="A8" s="13">
         <v>30010008</v>
       </c>
       <c r="B8">
@@ -4323,7 +4753,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="12">
+      <c r="A9" s="13">
         <v>30010009</v>
       </c>
       <c r="B9">
@@ -4331,7 +4761,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="12">
+      <c r="A10" s="13">
         <v>30010010</v>
       </c>
       <c r="B10">
@@ -4339,7 +4769,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="12">
+      <c r="A11" s="13">
         <v>30010011</v>
       </c>
       <c r="B11">
@@ -4347,7 +4777,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="12">
+      <c r="A12" s="13">
         <v>30010012</v>
       </c>
       <c r="B12">
@@ -4355,7 +4785,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="12">
+      <c r="A13" s="13">
         <v>30010013</v>
       </c>
       <c r="B13">
@@ -4363,7 +4793,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="12">
+      <c r="A14" s="13">
         <v>30010014</v>
       </c>
       <c r="B14">
@@ -4371,7 +4801,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="12">
+      <c r="A15" s="13">
         <v>30010015</v>
       </c>
       <c r="B15">
@@ -4379,7 +4809,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="12">
+      <c r="A16" s="13">
         <v>30010016</v>
       </c>
       <c r="B16">
@@ -4387,7 +4817,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="12">
+      <c r="A17" s="13">
         <v>30010017</v>
       </c>
       <c r="B17">
@@ -4395,7 +4825,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="12">
+      <c r="A18" s="13">
         <v>30010018</v>
       </c>
       <c r="B18">
@@ -4403,7 +4833,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="12">
+      <c r="A19" s="13">
         <v>30010019</v>
       </c>
       <c r="B19">
@@ -4411,7 +4841,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="12">
+      <c r="A20" s="13">
         <v>30010020</v>
       </c>
       <c r="B20">
@@ -4419,7 +4849,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="12">
+      <c r="A21" s="13">
         <v>30010021</v>
       </c>
       <c r="B21">
@@ -4427,7 +4857,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="12">
+      <c r="A22" s="13">
         <v>30010022</v>
       </c>
       <c r="B22">
@@ -4435,7 +4865,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="12">
+      <c r="A23" s="13">
         <v>30010001</v>
       </c>
       <c r="B23">
@@ -4443,7 +4873,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="12">
+      <c r="A24" s="13">
         <v>30010002</v>
       </c>
       <c r="B24">
@@ -4451,7 +4881,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="12">
+      <c r="A25" s="13">
         <v>30010003</v>
       </c>
       <c r="B25">
@@ -4459,7 +4889,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="12">
+      <c r="A26" s="13">
         <v>30010004</v>
       </c>
       <c r="B26">
@@ -4467,7 +4897,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="12">
+      <c r="A27" s="13">
         <v>30010005</v>
       </c>
       <c r="B27">
@@ -4475,7 +4905,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="12">
+      <c r="A28" s="13">
         <v>30010006</v>
       </c>
       <c r="B28">
@@ -4483,7 +4913,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="12">
+      <c r="A29" s="13">
         <v>30010007</v>
       </c>
       <c r="B29">
@@ -4491,7 +4921,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="12">
+      <c r="A30" s="13">
         <v>30010008</v>
       </c>
       <c r="B30">
@@ -4499,7 +4929,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="12">
+      <c r="A31" s="13">
         <v>30010009</v>
       </c>
       <c r="B31">
@@ -4507,7 +4937,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="12">
+      <c r="A32" s="13">
         <v>30010010</v>
       </c>
       <c r="B32">
@@ -4515,7 +4945,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="12">
+      <c r="A33" s="13">
         <v>30010011</v>
       </c>
       <c r="B33">
@@ -4523,7 +4953,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="12">
+      <c r="A34" s="13">
         <v>30010012</v>
       </c>
       <c r="B34">
@@ -4531,7 +4961,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="12">
+      <c r="A35" s="13">
         <v>30010013</v>
       </c>
       <c r="B35">
@@ -4539,7 +4969,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="12">
+      <c r="A36" s="13">
         <v>30010014</v>
       </c>
       <c r="B36">
@@ -4547,7 +4977,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="12">
+      <c r="A37" s="13">
         <v>30010015</v>
       </c>
       <c r="B37">
@@ -4555,7 +4985,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="12">
+      <c r="A38" s="13">
         <v>30010016</v>
       </c>
       <c r="B38">
@@ -4563,7 +4993,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="12">
+      <c r="A39" s="13">
         <v>30010017</v>
       </c>
       <c r="B39">
@@ -4571,7 +5001,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="12">
+      <c r="A40" s="13">
         <v>30010018</v>
       </c>
       <c r="B40">
@@ -4579,7 +5009,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="12">
+      <c r="A41" s="13">
         <v>30010019</v>
       </c>
       <c r="B41">
@@ -4587,7 +5017,7 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="12">
+      <c r="A42" s="13">
         <v>30010020</v>
       </c>
       <c r="B42">
@@ -4595,7 +5025,7 @@
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="12">
+      <c r="A43" s="13">
         <v>30010021</v>
       </c>
       <c r="B43">
@@ -4603,7 +5033,7 @@
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="12">
+      <c r="A44" s="13">
         <v>30010022</v>
       </c>
       <c r="B44">
@@ -5026,7 +5456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:8">
       <c r="A97">
         <v>20130211</v>
       </c>
@@ -5034,7 +5464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:8">
       <c r="A98">
         <v>20130311</v>
       </c>
@@ -5042,7 +5472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:8">
       <c r="A99">
         <v>20420111</v>
       </c>
@@ -5050,7 +5480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:8">
       <c r="A100">
         <v>20620111</v>
       </c>
@@ -5058,7 +5488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:8">
       <c r="A101">
         <v>20820111</v>
       </c>
@@ -5066,7 +5496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:8">
       <c r="A102">
         <v>20720111</v>
       </c>
@@ -5074,7 +5504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:8">
       <c r="A103">
         <v>20920111</v>
       </c>
@@ -5082,7 +5512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:8">
       <c r="A104">
         <v>60030004</v>
       </c>
@@ -5090,7 +5520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:8">
       <c r="A105">
         <v>60030011</v>
       </c>
@@ -5098,7 +5528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:8">
       <c r="A106">
         <v>60030003</v>
       </c>
@@ -5106,7 +5536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:8">
       <c r="A107">
         <v>60030002</v>
       </c>
@@ -5114,7 +5544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:8">
       <c r="A108">
         <v>60030008</v>
       </c>
@@ -5122,7 +5552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:8">
       <c r="A109">
         <v>60030010</v>
       </c>
@@ -5130,7 +5560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:8">
       <c r="A110">
         <v>60030001</v>
       </c>
@@ -5138,7 +5568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:8">
       <c r="A111">
         <v>60030009</v>
       </c>
@@ -5146,15 +5576,149 @@
         <v>1</v>
       </c>
     </row>
+    <row r="112" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A112" s="1">
+        <v>157</v>
+      </c>
+      <c r="B112" s="1">
+        <v>3000104</v>
+      </c>
+      <c r="C112" s="1">
+        <v>1</v>
+      </c>
+      <c r="D112" s="1">
+        <v>5</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="113" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A113" s="1">
+        <v>158</v>
+      </c>
+      <c r="B113" s="14">
+        <v>60030067</v>
+      </c>
+      <c r="C113" s="1">
+        <v>1</v>
+      </c>
+      <c r="D113" s="1">
+        <v>5</v>
+      </c>
+      <c r="E113" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="114" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A114" s="1">
+        <v>159</v>
+      </c>
+      <c r="B114" s="14">
+        <v>60030072</v>
+      </c>
+      <c r="C114" s="1">
+        <v>1</v>
+      </c>
+      <c r="D114" s="1">
+        <v>5</v>
+      </c>
+      <c r="E114" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="115" s="12" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A115" s="1">
+        <v>160</v>
+      </c>
+      <c r="B115" s="14">
+        <v>60030068</v>
+      </c>
+      <c r="C115" s="1">
+        <v>1</v>
+      </c>
+      <c r="D115" s="1">
+        <v>5</v>
+      </c>
+      <c r="E115" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="B113">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M113">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B114">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M114">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A115">
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B115">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M115">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A71:A73">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78:A80">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A90:A92">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A112:A114">
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -5312,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>32</v>
@@ -5341,16 +5905,16 @@
         <v>1</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -5370,16 +5934,16 @@
         <v>1</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
@@ -5400,16 +5964,16 @@
         <v>1</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="I8" s="1">
         <v>2</v>
@@ -5435,16 +5999,16 @@
         <v>1</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="I9" s="1">
         <v>2</v>
@@ -5470,16 +6034,16 @@
         <v>1</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
@@ -5499,16 +6063,16 @@
         <v>1</v>
       </c>
       <c r="E11" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
@@ -5532,16 +6096,16 @@
         <v>1</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I12" s="1">
         <v>2</v>
@@ -5567,16 +6131,16 @@
         <v>1</v>
       </c>
       <c r="E13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
@@ -5596,16 +6160,16 @@
         <v>1</v>
       </c>
       <c r="E14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="I14" s="1">
         <v>1</v>
@@ -5629,16 +6193,16 @@
         <v>1</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="I15" s="1">
         <v>2</v>
@@ -5664,16 +6228,16 @@
         <v>1</v>
       </c>
       <c r="E16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
@@ -5696,16 +6260,16 @@
         <v>1</v>
       </c>
       <c r="E17" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="I17" s="1">
         <v>1</v>
@@ -5730,7 +6294,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>32</v>
@@ -5763,7 +6327,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>32</v>
@@ -5772,7 +6336,7 @@
         <v>33</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
@@ -5796,16 +6360,16 @@
         <v>1</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
@@ -5829,16 +6393,16 @@
         <v>1</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
@@ -5862,16 +6426,16 @@
         <v>1</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
@@ -5895,16 +6459,16 @@
         <v>1</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I23" s="1">
         <v>1</v>
@@ -5928,16 +6492,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
@@ -5961,16 +6525,16 @@
         <v>1</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
@@ -5994,16 +6558,16 @@
         <v>1</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I26" s="1">
         <v>1</v>
@@ -6027,7 +6591,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>32</v>
@@ -6058,16 +6622,16 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I28" s="1">
         <v>2</v>
@@ -6089,16 +6653,16 @@
         <v>1</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I29" s="1">
         <v>2</v>
@@ -6120,7 +6684,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>32</v>
@@ -6129,7 +6693,7 @@
         <v>33</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I30" s="1">
         <v>2</v>
@@ -6151,13 +6715,13 @@
         <v>2</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N31" s="6"/>
       <c r="S31" s="6"/>
@@ -6176,13 +6740,13 @@
         <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N32" s="6"/>
       <c r="S32" s="6"/>
@@ -6201,13 +6765,13 @@
         <v>2</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N33" s="6"/>
       <c r="S33" s="6"/>
@@ -6226,13 +6790,13 @@
         <v>2</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N34" s="6"/>
       <c r="S34" s="6"/>
@@ -6251,13 +6815,13 @@
         <v>2</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N35" s="6"/>
       <c r="S35" s="6"/>
@@ -6276,13 +6840,13 @@
         <v>2</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N36" s="6"/>
       <c r="S36" s="6"/>
@@ -6301,13 +6865,13 @@
         <v>2</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N37" s="6"/>
       <c r="S37" s="6"/>
@@ -6326,13 +6890,13 @@
         <v>2</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N38" s="6"/>
       <c r="S38" s="6"/>
@@ -6351,13 +6915,13 @@
         <v>2</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N39" s="6"/>
       <c r="S39" s="6"/>
@@ -6376,11 +6940,11 @@
         <v>3</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="F40" s="6"/>
       <c r="H40" s="1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="N40" s="6"/>
       <c r="S40" s="6"/>
@@ -6399,11 +6963,11 @@
         <v>3</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="F41" s="6"/>
       <c r="H41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N41" s="6"/>
       <c r="S41" s="6"/>
@@ -6422,11 +6986,11 @@
         <v>3</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="F42" s="6"/>
       <c r="H42" s="1" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="N42" s="6"/>
       <c r="S42" s="6"/>
@@ -6445,11 +7009,11 @@
         <v>3</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="F43" s="6"/>
       <c r="H43" s="1" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="N43" s="6"/>
       <c r="S43" s="6"/>
@@ -6468,11 +7032,11 @@
         <v>3</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="F44" s="6"/>
       <c r="H44" s="1" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6489,11 +7053,11 @@
         <v>3</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="F45" s="6"/>
       <c r="H45" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:19">
@@ -6510,10 +7074,10 @@
         <v>3</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6530,11 +7094,11 @@
         <v>3</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="F47" s="6"/>
       <c r="H47" s="1" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6551,11 +7115,11 @@
         <v>4</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="F48" s="6"/>
       <c r="H48" s="1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6572,11 +7136,11 @@
         <v>4</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="F49" s="6"/>
       <c r="H49" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6593,11 +7157,11 @@
         <v>4</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="F50" s="6"/>
       <c r="H50" s="1" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6614,11 +7178,11 @@
         <v>4</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="F51" s="6"/>
       <c r="H51" s="1" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6635,11 +7199,11 @@
         <v>4</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="F52" s="6"/>
       <c r="H52" s="1" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6656,16 +7220,16 @@
         <v>5</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -6682,7 +7246,7 @@
         <v>5</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>32</v>
@@ -6711,16 +7275,16 @@
         <v>5</v>
       </c>
       <c r="E55" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F55" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="G55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="I55" s="1">
         <v>1</v>
@@ -6740,16 +7304,16 @@
         <v>5</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I56" s="1">
         <v>1</v>
@@ -6770,16 +7334,16 @@
         <v>5</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F57" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="I57" s="1">
         <v>2</v>
@@ -6805,16 +7369,16 @@
         <v>5</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="I58" s="1">
         <v>2</v>
@@ -6840,16 +7404,16 @@
         <v>5</v>
       </c>
       <c r="E59" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="I59" s="1">
         <v>1</v>
@@ -6869,16 +7433,16 @@
         <v>5</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="I60" s="1">
         <v>1</v>
@@ -6902,16 +7466,16 @@
         <v>5</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I61" s="1">
         <v>2</v>
@@ -6937,16 +7501,16 @@
         <v>5</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="I62" s="1">
         <v>1</v>
@@ -6966,16 +7530,16 @@
         <v>5</v>
       </c>
       <c r="E63" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="I63" s="1">
         <v>1</v>
@@ -6999,16 +7563,16 @@
         <v>5</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="I64" s="1">
         <v>2</v>
@@ -7034,16 +7598,16 @@
         <v>5</v>
       </c>
       <c r="E65" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="I65" s="1">
         <v>1</v>
@@ -7066,16 +7630,16 @@
         <v>5</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="I66" s="1">
         <v>1</v>
@@ -7100,7 +7664,7 @@
         <v>5</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>32</v>
@@ -7133,7 +7697,7 @@
         <v>5</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>32</v>
@@ -7142,7 +7706,7 @@
         <v>33</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I68" s="1">
         <v>1</v>
@@ -7166,16 +7730,16 @@
         <v>5</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I69" s="1">
         <v>1</v>
@@ -7199,16 +7763,16 @@
         <v>5</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I70" s="1">
         <v>1</v>
@@ -7232,16 +7796,16 @@
         <v>5</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F71" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I71" s="1">
         <v>1</v>
@@ -7265,16 +7829,16 @@
         <v>5</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I72" s="1">
         <v>1</v>
@@ -7298,16 +7862,16 @@
         <v>5</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F73" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I73" s="1">
         <v>1</v>
@@ -7331,16 +7895,16 @@
         <v>5</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I74" s="1">
         <v>1</v>
@@ -7364,16 +7928,16 @@
         <v>5</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I75" s="1">
         <v>1</v>
@@ -7397,7 +7961,7 @@
         <v>5</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>32</v>
@@ -7428,16 +7992,16 @@
         <v>5</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I77" s="1">
         <v>2</v>
@@ -7459,16 +8023,16 @@
         <v>5</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I78" s="1">
         <v>2</v>
@@ -7490,7 +8054,7 @@
         <v>5</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F79" s="6" t="s">
         <v>32</v>
@@ -7499,7 +8063,7 @@
         <v>33</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I79" s="1">
         <v>2</v>
